--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Projects\NAC-YOLO-Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61210C14-123B-4B72-8278-96844641831B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11955" windowHeight="10725" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wybrane obserwacje LROC NAC" sheetId="1" r:id="rId1"/>
@@ -34,18 +35,29 @@
     <definedName name="creater_sizes_8" localSheetId="3">'Metryki na LQ w rozmiarach'!$T$5:$X$7</definedName>
     <definedName name="creater_sizes_9" localSheetId="3">'Metryki na LQ w rozmiarach'!$T$4:$X$4</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="creater_sizes" type="6" refreshedVersion="6" background="1" saveData="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="creater_sizes" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -59,7 +71,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="2" name="creater_sizes1" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="2" xr16:uid="{00000000-0015-0000-FFFF-FFFF01000000}" name="creater_sizes1" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_downsampling_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -73,7 +85,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="3" name="creater_sizes11" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="3" xr16:uid="{00000000-0015-0000-FFFF-FFFF02000000}" name="creater_sizes11" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_downsampling_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -87,7 +99,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="4" name="creater_sizes12" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="4" xr16:uid="{00000000-0015-0000-FFFF-FFFF03000000}" name="creater_sizes12" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_downsampling_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -101,7 +113,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="5" name="creater_sizes121" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="5" xr16:uid="{00000000-0015-0000-FFFF-FFFF04000000}" name="creater_sizes121" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_downsampling_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -115,7 +127,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="6" name="creater_sizes1211" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="6" xr16:uid="{00000000-0015-0000-FFFF-FFFF05000000}" name="creater_sizes1211" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_downsampling_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -129,7 +141,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="7" name="creater_sizes1212" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="7" xr16:uid="{00000000-0015-0000-FFFF-FFFF06000000}" name="creater_sizes1212" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_downsampling_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -143,7 +155,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="8" name="creater_sizes2" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="8" xr16:uid="{00000000-0015-0000-FFFF-FFFF07000000}" name="creater_sizes2" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_blur_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -157,7 +169,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="9" name="creater_sizes21" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="9" xr16:uid="{00000000-0015-0000-FFFF-FFFF08000000}" name="creater_sizes21" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_blur_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -171,7 +183,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="10" name="creater_sizes22" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="10" xr16:uid="{00000000-0015-0000-FFFF-FFFF09000000}" name="creater_sizes22" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_blur_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -185,7 +197,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="11" name="creater_sizes221" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="11" xr16:uid="{00000000-0015-0000-FFFF-FFFF0A000000}" name="creater_sizes221" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_blur_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -199,7 +211,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="12" name="creater_sizes2211" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="12" xr16:uid="{00000000-0015-0000-FFFF-FFFF0B000000}" name="creater_sizes2211" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_blur_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -213,7 +225,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="13" name="creater_sizes2212" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="13" xr16:uid="{00000000-0015-0000-FFFF-FFFF0C000000}" name="creater_sizes2212" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_blur_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -227,7 +239,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="14" name="creater_sizes3" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="14" xr16:uid="{00000000-0015-0000-FFFF-FFFF0D000000}" name="creater_sizes3" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_summation_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -241,7 +253,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="15" name="creater_sizes31" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="15" xr16:uid="{00000000-0015-0000-FFFF-FFFF0E000000}" name="creater_sizes31" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_summation_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -255,7 +267,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="16" name="creater_sizes32" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="16" xr16:uid="{00000000-0015-0000-FFFF-FFFF0F000000}" name="creater_sizes32" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_summation_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -269,7 +281,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="17" name="creater_sizes321" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="17" xr16:uid="{00000000-0015-0000-FFFF-FFFF10000000}" name="creater_sizes321" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_summation_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -283,7 +295,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="18" name="creater_sizes3211" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="18" xr16:uid="{00000000-0015-0000-FFFF-FFFF11000000}" name="creater_sizes3211" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_summation_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -297,7 +309,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="19" name="creater_sizes3212" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="19" xr16:uid="{00000000-0015-0000-FFFF-FFFF12000000}" name="creater_sizes3212" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_summation_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -311,7 +323,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="20" name="creater_sizes4" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="20" xr16:uid="{00000000-0015-0000-FFFF-FFFF13000000}" name="creater_sizes4" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_all_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -325,7 +337,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="21" name="creater_sizes41" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="21" xr16:uid="{00000000-0015-0000-FFFF-FFFF14000000}" name="creater_sizes41" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_all_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -339,7 +351,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="22" name="creater_sizes42" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="22" xr16:uid="{00000000-0015-0000-FFFF-FFFF15000000}" name="creater_sizes42" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_all_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -353,7 +365,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="23" name="creater_sizes421" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="23" xr16:uid="{00000000-0015-0000-FFFF-FFFF16000000}" name="creater_sizes421" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_all_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -367,7 +379,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="24" name="creater_sizes4211" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="24" xr16:uid="{00000000-0015-0000-FFFF-FFFF17000000}" name="creater_sizes4211" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_all_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -381,7 +393,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="25" name="creater_sizes4212" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="25" xr16:uid="{00000000-0015-0000-FFFF-FFFF18000000}" name="creater_sizes4212" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_all_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -395,7 +407,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="26" name="creater_sizes5" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="26" xr16:uid="{00000000-0015-0000-FFFF-FFFF19000000}" name="creater_sizes5" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -409,7 +421,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="27" name="creater_sizes6" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="27" xr16:uid="{00000000-0015-0000-FFFF-FFFF1A000000}" name="creater_sizes6" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -423,7 +435,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="28" name="creater_sizes61" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="28" xr16:uid="{00000000-0015-0000-FFFF-FFFF1B000000}" name="creater_sizes61" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -437,7 +449,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="29" name="creater_sizes611" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="29" xr16:uid="{00000000-0015-0000-FFFF-FFFF1C000000}" name="creater_sizes611" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -451,7 +463,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="30" name="creater_sizes612" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="30" xr16:uid="{00000000-0015-0000-FFFF-FFFF1D000000}" name="creater_sizes612" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -768,7 +780,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -870,7 +882,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -882,18 +894,15 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -908,11 +917,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -920,22 +924,22 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1494,18 +1498,17 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BAA5175B-8872-407F-B607-BF9620C14B9D}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{29F527A0-FEF9-4233-BD69-04B11D49F338}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1518,7 +1521,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -1530,18 +1532,17 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C5A0A341-115E-4BA2-8587-391B7C53EB75}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{95AC7FF8-AE0D-4C13-AF69-DD828FBC223F}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1554,7 +1555,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -1566,18 +1566,17 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{09D3D339-9B39-49FA-9690-D1D2DFFB64F7}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{0BA6E71E-F51E-4669-A090-4CB09C2A7F4F}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1590,7 +1589,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -1602,18 +1600,17 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2360751F-1B35-457D-90DD-C8C2C773A936}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{C591520D-CAB9-438B-872D-278667A25597}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1626,7 +1623,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -1675,7 +1671,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showDataLabelsRange val="1"/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
@@ -1876,7 +1871,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2000,7 +1994,6 @@
         <c:idx val="6"/>
         <c:delete val="1"/>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2507,18 +2500,17 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{319B89F3-57E7-4D99-8B8D-E79FFB434046}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{072E9790-9A52-46A1-A84E-0538EC41434E}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2531,7 +2523,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -2543,18 +2534,17 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E50F1C0E-2C63-4908-A38C-903E1A1B9404}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{6BEC6EC6-3A90-43B6-8355-C275888A49DA}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2567,7 +2557,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -2579,18 +2568,17 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BE7D9CCC-978E-41F7-A98E-11039C772194}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{F4ECD5E9-3ADA-490C-BABC-DEA5E60BA5D0}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2603,7 +2591,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -2615,18 +2602,17 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A5006927-5154-4B17-BEE5-22CE0EF2073D}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{3FF86C36-D657-4726-AC2A-12AB9183B334}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2639,7 +2625,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -2688,7 +2673,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showDataLabelsRange val="1"/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
@@ -2899,7 +2883,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3023,7 +3006,6 @@
         <c:idx val="6"/>
         <c:delete val="1"/>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3528,18 +3510,17 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C5C1FBF3-C1DB-4D7E-96AD-D28ED68400AA}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{E321D94E-977C-4FD1-A355-0C664551D6BB}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3552,7 +3533,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -3564,18 +3544,17 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{454B73A4-E32F-433E-945F-339F9B7BCF70}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{6CC3E4F4-153D-4E6E-90A7-67460565A01F}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3588,7 +3567,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -3600,18 +3578,17 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0834BE1C-FD34-4250-88D0-19C6A8B75B80}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{A1FEFC66-42DC-4479-8FF7-49C3ACDC6ADF}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3624,7 +3601,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -3636,18 +3612,17 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{70B7F712-353E-4ED6-A9EB-E826A7C7AA1A}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{C9F71987-2566-40EB-A360-2B351E7EB367}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3660,7 +3635,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -3709,7 +3683,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showDataLabelsRange val="1"/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
@@ -3920,7 +3893,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -4044,7 +4016,6 @@
         <c:idx val="6"/>
         <c:delete val="1"/>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4551,18 +4522,17 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8542C7EB-DF6E-4BB8-A1C9-22BED782A3D7}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{06868FF4-B6B7-445D-AAB6-B136DDB2A802}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4575,7 +4545,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -4587,18 +4556,17 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{60220732-B854-480B-AAEE-DA55B5B0942B}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{F81D1158-7900-47D1-956B-AB0E205CEF0E}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4611,7 +4579,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -4623,18 +4590,17 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{68FE67E0-F233-4128-B53D-2D00249335E5}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{D9B3C41D-0413-4ABA-98A0-D1A6FCA80F8B}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4647,7 +4613,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -4659,18 +4624,17 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
-              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{363ED764-CDD4-4405-9D7B-8C7E217E5E64}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{581D2F6B-B3CF-4B83-98B2-D4D65FD05C5E}" type="CELLRANGE">
+                      <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US"/>
+                    <a:endParaRPr lang="pl-PL"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4683,7 +4647,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -4732,7 +4695,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showDataLabelsRange val="1"/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
@@ -4943,7 +4905,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -4969,7 +4930,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="pl-PL"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -5067,7 +5028,6 @@
         <c:idx val="6"/>
         <c:delete val="1"/>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5460,7 +5420,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -5586,7 +5545,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -5661,7 +5619,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6056,7 +6013,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -6190,7 +6146,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -6265,7 +6220,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6796,7 +6750,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -6871,7 +6824,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7314,7 +7266,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -7389,7 +7340,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11871,7 +11821,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Wykres 5"/>
+        <xdr:cNvPr id="6" name="Wykres 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -11901,7 +11857,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Wykres 6"/>
+        <xdr:cNvPr id="7" name="Wykres 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -11933,7 +11895,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Wykres 7"/>
+        <xdr:cNvPr id="8" name="Wykres 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -11965,7 +11933,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="9" name="Wykres 8"/>
+        <xdr:cNvPr id="9" name="Wykres 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -12358,7 +12332,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="15" name="Wykres 14"/>
+        <xdr:cNvPr id="15" name="Wykres 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -12388,7 +12368,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="16" name="Wykres 15"/>
+        <xdr:cNvPr id="16" name="Wykres 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -12415,12 +12401,18 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>231825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>79650</xdr:rowOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="17" name="Wykres 16"/>
+        <xdr:cNvPr id="17" name="Wykres 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -12450,7 +12442,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Wykres 1"/>
+        <xdr:cNvPr id="2" name="Wykres 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -12469,63 +12467,63 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes" connectionId="1" xr16:uid="{00000000-0016-0000-0300-00000E000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_12" connectionId="5" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_11" connectionId="28" xr16:uid="{00000000-0016-0000-0300-000005000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_1" connectionId="2" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_9" connectionId="27" xr16:uid="{00000000-0016-0000-0300-000004000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_14" connectionId="17" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_6" connectionId="16" xr16:uid="{00000000-0016-0000-0300-000003000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_3" connectionId="14" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_12" connectionId="5" xr16:uid="{00000000-0016-0000-0300-000002000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_9" connectionId="27" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_7" connectionId="10" xr16:uid="{00000000-0016-0000-0300-000001000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_13" connectionId="11" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_13" connectionId="11" xr16:uid="{00000000-0016-0000-0300-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_2" connectionId="8" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_1" connectionId="2" xr16:uid="{00000000-0016-0000-0300-00000D000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_10" connectionId="23" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_4" connectionId="20" xr16:uid="{00000000-0016-0000-0300-00000C000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_6" connectionId="16" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_2" connectionId="8" xr16:uid="{00000000-0016-0000-0300-00000B000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_7" connectionId="10" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_14" connectionId="17" xr16:uid="{00000000-0016-0000-0300-00000A000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_4" connectionId="20" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_8" connectionId="4" xr16:uid="{00000000-0016-0000-0300-000009000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_8" connectionId="4" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_3" connectionId="14" xr16:uid="{00000000-0016-0000-0300-000008000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_5" connectionId="22" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_5" connectionId="22" xr16:uid="{00000000-0016-0000-0300-000007000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_11" connectionId="28" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_10" connectionId="23" xr16:uid="{00000000-0016-0000-0300-000006000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12790,18 +12788,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="14" style="17" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" style="17" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="14" style="24" customWidth="1"/>
+    <col min="4" max="4" width="14" style="16" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="16" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" style="16" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="14" style="20" customWidth="1"/>
     <col min="9" max="9" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12840,25 +12838,25 @@
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="21">
         <v>0.59587928539432899</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="22">
         <v>66.88</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="21">
         <v>1.1399999999999999</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="22">
         <v>65.87</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="23" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12866,25 +12864,25 @@
       <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="21">
         <v>0.58256255764199005</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="22">
         <v>65.09</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="21">
         <v>1.7</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="22">
         <v>66.61</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="23" t="s">
         <v>66</v>
       </c>
     </row>
@@ -12892,25 +12890,25 @@
       <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="21">
         <v>0.59140474594205605</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="24">
         <v>64.94</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="21">
         <v>1.1399999999999999</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="22">
         <v>63.95</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="23" t="s">
         <v>67</v>
       </c>
     </row>
@@ -12918,25 +12916,25 @@
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="21">
         <v>0.58876450802762803</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="22">
         <v>62.88</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="21">
         <v>1.7</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="22">
         <v>64.42</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="23" t="s">
         <v>68</v>
       </c>
     </row>
@@ -12944,25 +12942,25 @@
       <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="21">
         <v>0.49227418493164998</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="22">
         <v>64.34</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="21">
         <v>1.1399999999999999</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="22">
         <v>63.27</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="23" t="s">
         <v>69</v>
       </c>
     </row>
@@ -12970,25 +12968,25 @@
       <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="21">
         <v>0.49439722050231499</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="22">
         <v>64.91</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="21">
         <v>1.69</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="22">
         <v>66.45</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H9" s="25" t="s">
         <v>70</v>
       </c>
     </row>
@@ -12996,25 +12994,25 @@
       <c r="A10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="21">
         <v>0.49933420700105502</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="22">
         <v>65.180000000000007</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="21">
         <v>1.1399999999999999</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="22">
         <v>64.11</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="25" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13022,25 +13020,25 @@
       <c r="A11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="22" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="21">
         <v>2.18856679415771</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="22">
         <v>71.08</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="21">
         <v>1.74</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="22">
         <v>72.78</v>
       </c>
-      <c r="H11" s="29" t="s">
+      <c r="H11" s="25" t="s">
         <v>71</v>
       </c>
     </row>
@@ -13048,25 +13046,25 @@
       <c r="A12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="22" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="26">
         <v>2.1245861832302002</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="22">
         <v>71.47</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="21">
         <v>1.18</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="24">
         <v>70.34</v>
       </c>
-      <c r="H12" s="29" t="s">
+      <c r="H12" s="25" t="s">
         <v>72</v>
       </c>
     </row>
@@ -13074,99 +13072,99 @@
       <c r="A13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="22" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="21">
         <v>2.1095564090528698</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="22">
         <v>70.81</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="21">
         <v>1.74</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="22">
         <v>72.52</v>
       </c>
-      <c r="H13" s="29" t="s">
+      <c r="H13" s="25" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
     </row>
     <row r="24" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13174,7 +13172,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13190,23 +13188,23 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="11" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -13226,7 +13224,7 @@
         <f t="shared" ref="D4:D9" si="0">32*(ROUNDUP(C4/32,0))</f>
         <v>512</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <f>ROUND(640/D4,2)</f>
         <v>1.25</v>
       </c>
@@ -13250,7 +13248,7 @@
         <f t="shared" si="0"/>
         <v>512</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <f t="shared" ref="E5:E13" si="2">ROUND(640/D5,2)</f>
         <v>1.25</v>
       </c>
@@ -13274,7 +13272,7 @@
         <f t="shared" si="0"/>
         <v>320</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
@@ -13298,7 +13296,7 @@
         <f t="shared" si="0"/>
         <v>512</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <f t="shared" si="2"/>
         <v>1.25</v>
       </c>
@@ -13322,7 +13320,7 @@
         <f t="shared" si="0"/>
         <v>640</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="3">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -13346,7 +13344,7 @@
         <f t="shared" si="0"/>
         <v>640</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="3">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -13370,7 +13368,7 @@
         <f>32*(ROUNDUP(C10/32,0))</f>
         <v>640</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="3">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -13394,7 +13392,7 @@
         <f t="shared" ref="D11:D13" si="3">32*(ROUNDUP(C11/32,0))</f>
         <v>192</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="3">
         <f t="shared" si="2"/>
         <v>3.33</v>
       </c>
@@ -13418,7 +13416,7 @@
         <f t="shared" si="3"/>
         <v>192</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="3">
         <f t="shared" si="2"/>
         <v>3.33</v>
       </c>
@@ -13442,7 +13440,7 @@
         <f t="shared" si="3"/>
         <v>192</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="3">
         <f t="shared" si="2"/>
         <v>3.33</v>
       </c>
@@ -13503,11 +13501,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AM40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13533,314 +13532,314 @@
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="J4" s="22" t="s">
+      <c r="J4" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="L4" s="22" t="s">
+      <c r="L4" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="22" t="s">
+      <c r="M4" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="P4" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="Q4" s="15" t="s">
+      <c r="Q4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="R4" s="15" t="s">
+      <c r="R4" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="S4" s="15" t="s">
+      <c r="S4" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="T4" s="15" t="s">
+      <c r="T4" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="U4" s="15" t="s">
+      <c r="U4" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="X4" s="15" t="s">
+      <c r="X4" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="Y4" s="15" t="s">
+      <c r="Y4" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="Z4" s="15" t="s">
+      <c r="Z4" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="AA4" s="15" t="s">
+      <c r="AA4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="AB4" s="15" t="s">
+      <c r="AB4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AC4" s="15" t="s">
+      <c r="AC4" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="AD4" s="15" t="s">
+      <c r="AD4" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AG4" s="15" t="s">
+      <c r="AG4" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="AH4" s="15" t="s">
+      <c r="AH4" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="AI4" s="15" t="s">
+      <c r="AI4" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="AJ4" s="15" t="s">
+      <c r="AJ4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="AK4" s="15" t="s">
+      <c r="AK4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AL4" s="15" t="s">
+      <c r="AL4" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="AM4" s="15" t="s">
+      <c r="AM4" s="14" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="15">
         <v>0.75995799404126396</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="15">
         <v>0.75903614457831303</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="15">
         <v>0.79762583741197302</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="15">
         <v>0.50433843829828395</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="I5" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="19">
         <f>ROUND(0.759957994041264,3)</f>
         <v>0.76</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="19">
         <f>ROUND(0.759036144578313,3)</f>
         <v>0.75900000000000001</v>
       </c>
-      <c r="L5" s="23">
+      <c r="L5" s="19">
         <f>ROUND(0.797625837411973,3)</f>
         <v>0.79800000000000004</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="19">
         <f>ROUND(0.504338438298284,3)</f>
         <v>0.504</v>
       </c>
       <c r="P5" t="s">
         <v>85</v>
       </c>
-      <c r="Q5" s="17" t="s">
+      <c r="Q5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="18">
+      <c r="R5" s="17">
         <f>(C7-$J$5)/$J$5</f>
         <v>-4.4864586214922376E-2</v>
       </c>
-      <c r="S5" s="18">
+      <c r="S5" s="17">
         <f>(D7-$K$5)/$K$5</f>
         <v>1.7948910672371459E-2</v>
       </c>
-      <c r="T5" s="18">
+      <c r="T5" s="17">
         <f>(E7-$L$5)/$L$5</f>
         <v>3.6021074538602642E-2</v>
       </c>
-      <c r="U5" s="18">
+      <c r="U5" s="17">
         <f>(F7-$M$5)/$M$5</f>
         <v>4.5718648213859056E-2</v>
       </c>
       <c r="X5" t="s">
         <v>85</v>
       </c>
-      <c r="Y5" s="17">
+      <c r="Y5" s="16">
         <v>1</v>
       </c>
-      <c r="Z5" s="35">
+      <c r="Z5" s="31">
         <f>MIN($AA$5:$AB$8)-1%</f>
         <v>-0.28592643218061181</v>
       </c>
-      <c r="AA5" s="18">
+      <c r="AA5" s="17">
         <v>-4.4864586214922376E-2</v>
       </c>
-      <c r="AB5" s="18">
+      <c r="AB5" s="17">
         <v>0.24831661785313733</v>
       </c>
-      <c r="AC5" s="34">
+      <c r="AC5" s="30">
         <f>Y5</f>
         <v>1</v>
       </c>
-      <c r="AD5" s="18">
+      <c r="AD5" s="17">
         <f>AA5</f>
         <v>-4.4864586214922376E-2</v>
       </c>
       <c r="AG5" t="s">
         <v>85</v>
       </c>
-      <c r="AH5" s="17">
+      <c r="AH5" s="16">
         <v>1</v>
       </c>
-      <c r="AI5" s="35">
+      <c r="AI5" s="31">
         <f>MIN($AJ$5:$AK$8)-31%</f>
         <v>-0.3849286187770114</v>
       </c>
-      <c r="AJ5" s="18">
+      <c r="AJ5" s="17">
         <v>3.6021074538602642E-2</v>
       </c>
-      <c r="AK5" s="18">
+      <c r="AK5" s="17">
         <v>1.899023224865569</v>
       </c>
-      <c r="AL5" s="34">
+      <c r="AL5" s="30">
         <f>AH5</f>
         <v>1</v>
       </c>
-      <c r="AM5" s="18">
+      <c r="AM5" s="17">
         <f>AJ5</f>
         <v>3.6021074538602642E-2</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="15">
         <v>0.54612367336679901</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="15">
         <v>0.228440890919474</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="15">
         <v>0.26029666976078703</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="15">
         <v>8.1417102195645005E-2</v>
       </c>
-      <c r="I6" s="33" t="s">
+      <c r="I6" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="23">
+      <c r="J6" s="19">
         <f>ROUND(0.546123673366799,3)</f>
         <v>0.54600000000000004</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="19">
         <f>ROUND(0.228440890919474,3)</f>
         <v>0.22800000000000001</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="19">
         <f>ROUND(0.260296669760787,3)</f>
         <v>0.26</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="19">
         <f>ROUND(0.081417102195645,3)</f>
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="P6" t="s">
         <v>85</v>
       </c>
-      <c r="Q6" s="17" t="s">
+      <c r="Q6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="R6" s="18">
+      <c r="R6" s="17">
         <f>(C8-$J$6)/$J$6</f>
         <v>0.24831661785313733</v>
       </c>
-      <c r="S6" s="18">
+      <c r="S6" s="17">
         <f>(D8-$K$6)/$K$6</f>
         <v>2.0239624696879037</v>
       </c>
-      <c r="T6" s="18">
+      <c r="T6" s="17">
         <f>(E8-$L$6)/$L$6</f>
         <v>1.899023224865569</v>
       </c>
-      <c r="U6" s="18">
+      <c r="U6" s="17">
         <f>(F8-$M$6)/$M$6</f>
         <v>4.5079599717251355</v>
       </c>
       <c r="X6" t="s">
         <v>74</v>
       </c>
-      <c r="Y6" s="17">
+      <c r="Y6" s="16">
         <v>2</v>
       </c>
-      <c r="Z6" s="35">
+      <c r="Z6" s="31">
         <f t="shared" ref="Z6:Z8" si="0">MIN($AA$5:$AB$8)-1%</f>
         <v>-0.28592643218061181</v>
       </c>
-      <c r="AA6" s="18">
+      <c r="AA6" s="17">
         <v>4.5827154474381866E-3</v>
       </c>
-      <c r="AB6" s="18">
+      <c r="AB6" s="17">
         <v>-0.1997633493290239</v>
       </c>
-      <c r="AC6" s="34">
+      <c r="AC6" s="30">
         <f>Y5</f>
         <v>1</v>
       </c>
-      <c r="AD6" s="18">
+      <c r="AD6" s="17">
         <f>AB5</f>
         <v>0.24831661785313733</v>
       </c>
       <c r="AG6" t="s">
         <v>74</v>
       </c>
-      <c r="AH6" s="17">
+      <c r="AH6" s="16">
         <v>2</v>
       </c>
-      <c r="AI6" s="35">
+      <c r="AI6" s="31">
         <f t="shared" ref="AI6:AI8" si="1">MIN($AJ$5:$AK$8)-31%</f>
         <v>-0.3849286187770114</v>
       </c>
-      <c r="AJ6" s="18">
+      <c r="AJ6" s="17">
         <v>6.3229734812736763E-2</v>
       </c>
-      <c r="AK6" s="18">
+      <c r="AK6" s="17">
         <v>0.15809703700931527</v>
       </c>
-      <c r="AL6" s="34">
+      <c r="AL6" s="30">
         <f>AH5</f>
         <v>1</v>
       </c>
-      <c r="AM6" s="18">
+      <c r="AM6" s="17">
         <f>AK5</f>
         <v>1.899023224865569</v>
       </c>
@@ -13849,88 +13848,88 @@
       <c r="A7" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="15">
         <v>0.725902914476659</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>0.77262322320032994</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="15">
         <v>0.82674481748180495</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="15">
         <v>0.52704219869978497</v>
       </c>
       <c r="P7" t="s">
         <v>74</v>
       </c>
-      <c r="Q7" s="17" t="s">
+      <c r="Q7" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="R7" s="18">
+      <c r="R7" s="17">
         <f>(C9-$J$5)/$J$5</f>
         <v>4.5827154474381866E-3</v>
       </c>
-      <c r="S7" s="18">
+      <c r="S7" s="17">
         <f>(D9-$K$5)/$K$5</f>
         <v>4.7668936616029042E-2</v>
       </c>
-      <c r="T7" s="18">
+      <c r="T7" s="17">
         <f>(E9-$L$5)/$L$5</f>
         <v>6.3229734812736763E-2</v>
       </c>
-      <c r="U7" s="18">
+      <c r="U7" s="17">
         <f>(F9-$M$5)/$M$5</f>
         <v>8.8731299356494139E-2</v>
       </c>
       <c r="X7" t="s">
         <v>50</v>
       </c>
-      <c r="Y7" s="17">
+      <c r="Y7" s="16">
         <v>3</v>
       </c>
-      <c r="Z7" s="35">
+      <c r="Z7" s="31">
         <f t="shared" si="0"/>
         <v>-0.28592643218061181</v>
       </c>
-      <c r="AA7" s="18">
+      <c r="AA7" s="17">
         <v>-8.0320909626405285E-2</v>
       </c>
-      <c r="AB7" s="18">
+      <c r="AB7" s="17">
         <v>-0.2759264321806118</v>
       </c>
-      <c r="AC7" s="34">
+      <c r="AC7" s="30">
         <f>Y6</f>
         <v>2</v>
       </c>
-      <c r="AD7" s="18">
+      <c r="AD7" s="17">
         <f>AA6</f>
         <v>4.5827154474381866E-3</v>
       </c>
       <c r="AG7" t="s">
         <v>50</v>
       </c>
-      <c r="AH7" s="17">
+      <c r="AH7" s="16">
         <v>3</v>
       </c>
-      <c r="AI7" s="35">
+      <c r="AI7" s="31">
         <f t="shared" si="1"/>
         <v>-0.3849286187770114</v>
       </c>
-      <c r="AJ7" s="18">
+      <c r="AJ7" s="17">
         <v>-7.4928618777011388E-2</v>
       </c>
-      <c r="AK7" s="18">
+      <c r="AK7" s="17">
         <v>-7.3656107730099993E-2</v>
       </c>
-      <c r="AL7" s="34">
+      <c r="AL7" s="30">
         <f>AH6</f>
         <v>2</v>
       </c>
-      <c r="AM7" s="18">
+      <c r="AM7" s="17">
         <f>AJ6</f>
         <v>6.3229734812736763E-2</v>
       </c>
@@ -13939,88 +13938,88 @@
       <c r="A8" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="15">
         <v>0.68158087334781303</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <v>0.689463443088842</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <v>0.75374603846504795</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>0.446144757709736</v>
       </c>
       <c r="P8" t="s">
         <v>74</v>
       </c>
-      <c r="Q8" s="17" t="s">
+      <c r="Q8" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="R8" s="18">
+      <c r="R8" s="17">
         <f>(C10-$J$6)/$J$6</f>
         <v>-0.1997633493290239</v>
       </c>
-      <c r="S8" s="18">
+      <c r="S8" s="17">
         <f>(D10-$K$6)/$K$6</f>
         <v>0.46031841454006128</v>
       </c>
-      <c r="T8" s="18">
+      <c r="T8" s="17">
         <f>(E10-$L$6)/$L$6</f>
         <v>0.15809703700931527</v>
       </c>
-      <c r="U8" s="18">
+      <c r="U8" s="17">
         <f>(F10-$M$6)/$M$6</f>
         <v>0.57491039408683964</v>
       </c>
       <c r="X8" t="s">
         <v>84</v>
       </c>
-      <c r="Y8" s="17">
+      <c r="Y8" s="16">
         <v>4</v>
       </c>
-      <c r="Z8" s="35">
+      <c r="Z8" s="31">
         <f t="shared" si="0"/>
         <v>-0.28592643218061181</v>
       </c>
-      <c r="AA8" s="18">
+      <c r="AA8" s="17">
         <v>1.4035673399938112E-2</v>
       </c>
-      <c r="AB8" s="18">
+      <c r="AB8" s="17">
         <v>0.20352189552526356</v>
       </c>
-      <c r="AC8" s="34">
+      <c r="AC8" s="30">
         <f>Y6</f>
         <v>2</v>
       </c>
-      <c r="AD8" s="18">
+      <c r="AD8" s="17">
         <f>AB6</f>
         <v>-0.1997633493290239</v>
       </c>
       <c r="AG8" t="s">
         <v>84</v>
       </c>
-      <c r="AH8" s="17">
+      <c r="AH8" s="16">
         <v>4</v>
       </c>
-      <c r="AI8" s="35">
+      <c r="AI8" s="31">
         <f t="shared" si="1"/>
         <v>-0.3849286187770114</v>
       </c>
-      <c r="AJ8" s="18">
+      <c r="AJ8" s="17">
         <v>3.800963360395232E-2</v>
       </c>
-      <c r="AK8" s="18">
+      <c r="AK8" s="17">
         <v>1.7615033682025305</v>
       </c>
-      <c r="AL8" s="34">
+      <c r="AL8" s="30">
         <f>AH6</f>
         <v>2</v>
       </c>
-      <c r="AM8" s="18">
+      <c r="AM8" s="17">
         <f>AK6</f>
         <v>0.15809703700931527</v>
       </c>
@@ -14029,56 +14028,56 @@
       <c r="A9" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="15">
         <v>0.76348286374005303</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>0.79518072289156605</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <v>0.84845732838056398</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>0.54872057487567305</v>
       </c>
       <c r="P9" t="s">
         <v>50</v>
       </c>
-      <c r="Q9" s="17" t="s">
+      <c r="Q9" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="R9" s="18">
+      <c r="R9" s="17">
         <f>(C11-$J$5)/$J$5</f>
         <v>-8.0320909626405285E-2</v>
       </c>
-      <c r="S9" s="18">
+      <c r="S9" s="17">
         <f>(D11-$K$5)/$K$5</f>
         <v>-0.10993494021257308</v>
       </c>
-      <c r="T9" s="18">
+      <c r="T9" s="17">
         <f>(E11-$L$5)/$L$5</f>
         <v>-7.4928618777011388E-2</v>
       </c>
-      <c r="U9" s="18">
+      <c r="U9" s="17">
         <f>(F11-$M$5)/$M$5</f>
         <v>-0.14498353809622816</v>
       </c>
-      <c r="AC9" s="34">
+      <c r="AC9" s="30">
         <f>Y7</f>
         <v>3</v>
       </c>
-      <c r="AD9" s="18">
+      <c r="AD9" s="17">
         <f>AA7</f>
         <v>-8.0320909626405285E-2</v>
       </c>
-      <c r="AL9" s="34">
+      <c r="AL9" s="30">
         <f>AH7</f>
         <v>3</v>
       </c>
-      <c r="AM9" s="18">
+      <c r="AM9" s="17">
         <f>AJ7</f>
         <v>-7.4928618777011388E-2</v>
       </c>
@@ -14087,60 +14086,60 @@
       <c r="A10" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="15">
         <v>0.43692921126635298</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="15">
         <v>0.33295259851513398</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="15">
         <v>0.30110522962242198</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>0.12756774192103401</v>
       </c>
       <c r="P10" t="s">
         <v>50</v>
       </c>
-      <c r="Q10" s="17" t="s">
+      <c r="Q10" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="R10" s="18">
+      <c r="R10" s="17">
         <f>(C12-$J$6)/$J$6</f>
         <v>-0.2759264321806118</v>
       </c>
-      <c r="S10" s="18">
+      <c r="S10" s="17">
         <f>(D12-$K$6)/$K$6</f>
         <v>0.59557946837396036</v>
       </c>
-      <c r="T10" s="18">
+      <c r="T10" s="17">
         <f>(E12-$L$6)/$L$6</f>
         <v>-7.3656107730099993E-2</v>
       </c>
-      <c r="U10" s="18">
+      <c r="U10" s="17">
         <f>(F12-$M$6)/$M$6</f>
         <v>-0.35597255211007783</v>
       </c>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="17"/>
-      <c r="AC10" s="34">
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AC10" s="30">
         <f>Y7</f>
         <v>3</v>
       </c>
-      <c r="AD10" s="18">
+      <c r="AD10" s="17">
         <f>AB7</f>
         <v>-0.2759264321806118</v>
       </c>
-      <c r="AH10" s="17"/>
-      <c r="AI10" s="17"/>
-      <c r="AL10" s="34">
+      <c r="AH10" s="16"/>
+      <c r="AI10" s="16"/>
+      <c r="AL10" s="30">
         <f>AH7</f>
         <v>3</v>
       </c>
-      <c r="AM10" s="18">
+      <c r="AM10" s="17">
         <f>AK7</f>
         <v>-7.3656107730099993E-2</v>
       </c>
@@ -14149,56 +14148,56 @@
       <c r="A11" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="15">
         <v>0.69895610868393199</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <v>0.67555938037865704</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>0.73820696221594495</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>0.43092829679950101</v>
       </c>
       <c r="P11" t="s">
         <v>84</v>
       </c>
-      <c r="Q11" s="17" t="s">
+      <c r="Q11" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="R11" s="18">
+      <c r="R11" s="17">
         <f>(C13-$J$5)/$J$5</f>
         <v>1.4035673399938112E-2</v>
       </c>
-      <c r="S11" s="18">
+      <c r="S11" s="17">
         <f>(D13-$K$5)/$K$5</f>
         <v>2.0938509024440652E-3</v>
       </c>
-      <c r="T11" s="18">
+      <c r="T11" s="17">
         <f>(E13-$L$5)/$L$5</f>
         <v>3.800963360395232E-2</v>
       </c>
-      <c r="U11" s="18">
+      <c r="U11" s="17">
         <f>(F13-$M$5)/$M$5</f>
         <v>5.1908974160972107E-2</v>
       </c>
-      <c r="AC11" s="34">
+      <c r="AC11" s="30">
         <f>Y8</f>
         <v>4</v>
       </c>
-      <c r="AD11" s="18">
+      <c r="AD11" s="17">
         <f>AA8</f>
         <v>1.4035673399938112E-2</v>
       </c>
-      <c r="AL11" s="34">
+      <c r="AL11" s="30">
         <f>AH8</f>
         <v>4</v>
       </c>
-      <c r="AM11" s="18">
+      <c r="AM11" s="17">
         <f>AJ8</f>
         <v>3.800963360395232E-2</v>
       </c>
@@ -14207,60 +14206,60 @@
       <c r="A12" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="15">
         <v>0.39534416802938599</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <v>0.36379211878926299</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <v>0.24084941199017401</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>5.2166223279083698E-2</v>
       </c>
       <c r="P12" t="s">
         <v>84</v>
       </c>
-      <c r="Q12" s="17" t="s">
+      <c r="Q12" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="R12" s="18">
+      <c r="R12" s="17">
         <f>(C14-$J$6)/$J$6</f>
         <v>0.20352189552526356</v>
       </c>
-      <c r="S12" s="18">
+      <c r="S12" s="17">
         <f>(D14-$K$6)/$K$6</f>
         <v>2.1736250964361186</v>
       </c>
-      <c r="T12" s="18">
+      <c r="T12" s="17">
         <f>(E14-$L$6)/$L$6</f>
         <v>1.7615033682025305</v>
       </c>
-      <c r="U12" s="18">
+      <c r="U12" s="17">
         <f>(F14-$M$6)/$M$6</f>
         <v>3.9772269087838268</v>
       </c>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-      <c r="AC12" s="34">
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AC12" s="30">
         <f>Y8</f>
         <v>4</v>
       </c>
-      <c r="AD12" s="18">
+      <c r="AD12" s="17">
         <f>AB8</f>
         <v>0.20352189552526356</v>
       </c>
-      <c r="AH12" s="17"/>
-      <c r="AI12" s="17"/>
-      <c r="AL12" s="34">
+      <c r="AH12" s="16"/>
+      <c r="AI12" s="16"/>
+      <c r="AL12" s="30">
         <f>AH8</f>
         <v>4</v>
       </c>
-      <c r="AM12" s="18">
+      <c r="AM12" s="17">
         <f>AK8</f>
         <v>1.7615033682025305</v>
       </c>
@@ -14269,19 +14268,19 @@
       <c r="A13" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="15">
         <v>0.77066711178395297</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="15">
         <v>0.76058923283495505</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="15">
         <v>0.82833168761595399</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="15">
         <v>0.53016212297712995</v>
       </c>
     </row>
@@ -14289,240 +14288,236 @@
       <c r="A14" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="15">
         <v>0.65712295495679396</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="15">
         <v>0.72358652198743501</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="15">
         <v>0.71799087573265796</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>0.40315537961149001</v>
       </c>
-      <c r="Y14" s="17"/>
-      <c r="Z14" s="17"/>
-      <c r="AC14" s="16"/>
-      <c r="AD14" s="16"/>
+      <c r="Y14" s="16"/>
+      <c r="Z14" s="16"/>
+      <c r="AC14" s="15"/>
+      <c r="AD14" s="15"/>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="P15" s="13"/>
+      <c r="P15" s="12"/>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="14"/>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="18"/>
-      <c r="T17" s="18"/>
-      <c r="U17" s="18"/>
+      <c r="A17" s="12"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17"/>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="15"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="18"/>
-      <c r="S18" s="18"/>
-      <c r="T18" s="18"/>
-      <c r="U18" s="18"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="14"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="18"/>
-      <c r="T19" s="18"/>
-      <c r="U19" s="18"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A20" s="19"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="18"/>
-      <c r="S20" s="18"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B21" s="17"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="18"/>
-      <c r="S21" s="18"/>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B22" s="17"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="18"/>
-      <c r="S22" s="18"/>
-      <c r="T22" s="18"/>
-      <c r="U22" s="18"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B23" s="17"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="18"/>
-      <c r="S23" s="18"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="18"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="17"/>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B24" s="17"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="18"/>
-      <c r="S24" s="18"/>
-      <c r="T24" s="18"/>
-      <c r="U24" s="18"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B25" s="17"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B26" s="17"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B27" s="17"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="15"/>
-      <c r="AA27" s="15"/>
-      <c r="AB27" s="15"/>
-      <c r="AC27" s="13"/>
-      <c r="AD27" s="15"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="14"/>
+      <c r="AB27" s="14"/>
+      <c r="AC27" s="12"/>
+      <c r="AD27" s="14"/>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B28" s="17"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="X28" s="19"/>
-      <c r="Y28" s="20"/>
-      <c r="Z28" s="20"/>
-      <c r="AA28" s="21"/>
-      <c r="AB28" s="21"/>
-      <c r="AC28" s="21"/>
-      <c r="AD28" s="21"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="Y28" s="16"/>
+      <c r="Z28" s="16"/>
+      <c r="AA28" s="15"/>
+      <c r="AB28" s="15"/>
+      <c r="AC28" s="15"/>
+      <c r="AD28" s="15"/>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="X29" s="19"/>
-      <c r="Y29" s="20"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="21"/>
-      <c r="AB29" s="21"/>
-      <c r="AC29" s="21"/>
-      <c r="AD29" s="21"/>
+      <c r="Y29" s="16"/>
+      <c r="Z29" s="16"/>
+      <c r="AA29" s="15"/>
+      <c r="AB29" s="15"/>
+      <c r="AC29" s="15"/>
+      <c r="AD29" s="15"/>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="Y30" s="17"/>
-      <c r="Z30" s="17"/>
-      <c r="AA30" s="21"/>
-      <c r="AB30" s="16"/>
-      <c r="AC30" s="16"/>
-      <c r="AD30" s="16"/>
+      <c r="Y30" s="16"/>
+      <c r="Z30" s="16"/>
+      <c r="AA30" s="15"/>
+      <c r="AB30" s="15"/>
+      <c r="AC30" s="15"/>
+      <c r="AD30" s="15"/>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="Y31" s="17"/>
-      <c r="Z31" s="17"/>
-      <c r="AA31" s="16"/>
-      <c r="AB31" s="16"/>
-      <c r="AC31" s="16"/>
-      <c r="AD31" s="16"/>
+      <c r="Y31" s="16"/>
+      <c r="Z31" s="16"/>
+      <c r="AA31" s="15"/>
+      <c r="AB31" s="15"/>
+      <c r="AC31" s="15"/>
+      <c r="AD31" s="15"/>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="X32" s="15" t="s">
+      <c r="X32" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="Y32" s="15" t="s">
+      <c r="Y32" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="Z32" s="15" t="s">
+      <c r="Z32" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="AA32" s="15" t="s">
+      <c r="AA32" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="AB32" s="15" t="s">
+      <c r="AB32" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AC32" s="15" t="s">
+      <c r="AC32" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="AD32" s="15" t="s">
+      <c r="AD32" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AG32" s="15" t="s">
+      <c r="AG32" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="AH32" s="15" t="s">
+      <c r="AH32" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="AI32" s="15" t="s">
+      <c r="AI32" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="AJ32" s="15" t="s">
+      <c r="AJ32" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="AK32" s="15" t="s">
+      <c r="AK32" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AL32" s="15" t="s">
+      <c r="AL32" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="AM32" s="15" t="s">
+      <c r="AM32" s="14" t="s">
         <v>82</v>
       </c>
     </row>
@@ -14530,50 +14525,50 @@
       <c r="X33" t="s">
         <v>85</v>
       </c>
-      <c r="Y33" s="17">
+      <c r="Y33" s="16">
         <v>1</v>
       </c>
-      <c r="Z33" s="35">
+      <c r="Z33" s="31">
         <f>MIN($AA$33:$AB$36)-26%</f>
         <v>-0.36993494021257312</v>
       </c>
-      <c r="AA33" s="18">
+      <c r="AA33" s="17">
         <v>1.7948910672371459E-2</v>
       </c>
-      <c r="AB33" s="18">
+      <c r="AB33" s="17">
         <v>2.0239624696879037</v>
       </c>
-      <c r="AC33" s="34">
+      <c r="AC33" s="30">
         <f>Y33</f>
         <v>1</v>
       </c>
-      <c r="AD33" s="18">
+      <c r="AD33" s="17">
         <f>AA33</f>
         <v>1.7948910672371459E-2</v>
       </c>
       <c r="AG33" t="s">
         <v>85</v>
       </c>
-      <c r="AH33" s="17">
+      <c r="AH33" s="16">
         <v>1</v>
       </c>
-      <c r="AI33" s="35">
+      <c r="AI33" s="31">
         <f>MIN($AJ$33:$AK$36)-38%</f>
         <v>-0.73597255211007784</v>
       </c>
-      <c r="AJ33" s="18">
+      <c r="AJ33" s="17">
         <f>U5</f>
         <v>4.5718648213859056E-2</v>
       </c>
-      <c r="AK33" s="18">
+      <c r="AK33" s="17">
         <f>U6</f>
         <v>4.5079599717251355</v>
       </c>
-      <c r="AL33" s="34">
+      <c r="AL33" s="30">
         <f>AH33</f>
         <v>1</v>
       </c>
-      <c r="AM33" s="18">
+      <c r="AM33" s="17">
         <f>AJ33</f>
         <v>4.5718648213859056E-2</v>
       </c>
@@ -14582,50 +14577,50 @@
       <c r="X34" t="s">
         <v>74</v>
       </c>
-      <c r="Y34" s="17">
+      <c r="Y34" s="16">
         <v>2</v>
       </c>
-      <c r="Z34" s="35">
+      <c r="Z34" s="31">
         <f t="shared" ref="Z34:Z36" si="2">MIN($AA$33:$AB$36)-26%</f>
         <v>-0.36993494021257312</v>
       </c>
-      <c r="AA34" s="18">
+      <c r="AA34" s="17">
         <v>4.7668936616029042E-2</v>
       </c>
-      <c r="AB34" s="18">
+      <c r="AB34" s="17">
         <v>0.46031841454006128</v>
       </c>
-      <c r="AC34" s="34">
+      <c r="AC34" s="30">
         <f>Y33</f>
         <v>1</v>
       </c>
-      <c r="AD34" s="18">
+      <c r="AD34" s="17">
         <f>AB33</f>
         <v>2.0239624696879037</v>
       </c>
       <c r="AG34" t="s">
         <v>74</v>
       </c>
-      <c r="AH34" s="17">
+      <c r="AH34" s="16">
         <v>2</v>
       </c>
-      <c r="AI34" s="35">
+      <c r="AI34" s="31">
         <f t="shared" ref="AI34:AI36" si="3">MIN($AJ$33:$AK$36)-38%</f>
         <v>-0.73597255211007784</v>
       </c>
-      <c r="AJ34" s="18">
+      <c r="AJ34" s="17">
         <f>U7</f>
         <v>8.8731299356494139E-2</v>
       </c>
-      <c r="AK34" s="18">
+      <c r="AK34" s="17">
         <f>U8</f>
         <v>0.57491039408683964</v>
       </c>
-      <c r="AL34" s="34">
+      <c r="AL34" s="30">
         <f>AH33</f>
         <v>1</v>
       </c>
-      <c r="AM34" s="18">
+      <c r="AM34" s="17">
         <f>AK33</f>
         <v>4.5079599717251355</v>
       </c>
@@ -14634,50 +14629,50 @@
       <c r="X35" t="s">
         <v>50</v>
       </c>
-      <c r="Y35" s="17">
+      <c r="Y35" s="16">
         <v>3</v>
       </c>
-      <c r="Z35" s="35">
+      <c r="Z35" s="31">
         <f t="shared" si="2"/>
         <v>-0.36993494021257312</v>
       </c>
-      <c r="AA35" s="18">
+      <c r="AA35" s="17">
         <v>-0.10993494021257308</v>
       </c>
-      <c r="AB35" s="18">
+      <c r="AB35" s="17">
         <v>0.59557946837396036</v>
       </c>
-      <c r="AC35" s="34">
+      <c r="AC35" s="30">
         <f>Y34</f>
         <v>2</v>
       </c>
-      <c r="AD35" s="18">
+      <c r="AD35" s="17">
         <f>AA34</f>
         <v>4.7668936616029042E-2</v>
       </c>
       <c r="AG35" t="s">
         <v>50</v>
       </c>
-      <c r="AH35" s="17">
+      <c r="AH35" s="16">
         <v>3</v>
       </c>
-      <c r="AI35" s="35">
+      <c r="AI35" s="31">
         <f t="shared" si="3"/>
         <v>-0.73597255211007784</v>
       </c>
-      <c r="AJ35" s="18">
+      <c r="AJ35" s="17">
         <f>U9</f>
         <v>-0.14498353809622816</v>
       </c>
-      <c r="AK35" s="18">
+      <c r="AK35" s="17">
         <f>U10</f>
         <v>-0.35597255211007783</v>
       </c>
-      <c r="AL35" s="34">
+      <c r="AL35" s="30">
         <f>AH34</f>
         <v>2</v>
       </c>
-      <c r="AM35" s="18">
+      <c r="AM35" s="17">
         <f>AJ34</f>
         <v>8.8731299356494139E-2</v>
       </c>
@@ -14686,138 +14681,138 @@
       <c r="X36" t="s">
         <v>84</v>
       </c>
-      <c r="Y36" s="17">
+      <c r="Y36" s="16">
         <v>4</v>
       </c>
-      <c r="Z36" s="35">
+      <c r="Z36" s="31">
         <f t="shared" si="2"/>
         <v>-0.36993494021257312</v>
       </c>
-      <c r="AA36" s="18">
+      <c r="AA36" s="17">
         <v>2.0938509024440652E-3</v>
       </c>
-      <c r="AB36" s="18">
+      <c r="AB36" s="17">
         <v>2.1736250964361186</v>
       </c>
-      <c r="AC36" s="34">
+      <c r="AC36" s="30">
         <f>Y34</f>
         <v>2</v>
       </c>
-      <c r="AD36" s="18">
+      <c r="AD36" s="17">
         <f>AB34</f>
         <v>0.46031841454006128</v>
       </c>
       <c r="AG36" t="s">
         <v>84</v>
       </c>
-      <c r="AH36" s="17">
+      <c r="AH36" s="16">
         <v>4</v>
       </c>
-      <c r="AI36" s="35">
+      <c r="AI36" s="31">
         <f t="shared" si="3"/>
         <v>-0.73597255211007784</v>
       </c>
-      <c r="AJ36" s="18">
+      <c r="AJ36" s="17">
         <f>U11</f>
         <v>5.1908974160972107E-2</v>
       </c>
-      <c r="AK36" s="18">
+      <c r="AK36" s="17">
         <f>U12</f>
         <v>3.9772269087838268</v>
       </c>
-      <c r="AL36" s="34">
+      <c r="AL36" s="30">
         <f>AH34</f>
         <v>2</v>
       </c>
-      <c r="AM36" s="18">
+      <c r="AM36" s="17">
         <f>AK34</f>
         <v>0.57491039408683964</v>
       </c>
     </row>
     <row r="37" spans="24:39" x14ac:dyDescent="0.25">
-      <c r="AC37" s="34">
+      <c r="AC37" s="30">
         <f>Y35</f>
         <v>3</v>
       </c>
-      <c r="AD37" s="18">
+      <c r="AD37" s="17">
         <f>AA35</f>
         <v>-0.10993494021257308</v>
       </c>
-      <c r="AL37" s="34">
+      <c r="AL37" s="30">
         <f>AH35</f>
         <v>3</v>
       </c>
-      <c r="AM37" s="18">
+      <c r="AM37" s="17">
         <f>AJ35</f>
         <v>-0.14498353809622816</v>
       </c>
     </row>
     <row r="38" spans="24:39" x14ac:dyDescent="0.25">
-      <c r="Y38" s="17"/>
-      <c r="Z38" s="17"/>
-      <c r="AC38" s="34">
+      <c r="Y38" s="16"/>
+      <c r="Z38" s="16"/>
+      <c r="AC38" s="30">
         <f>Y35</f>
         <v>3</v>
       </c>
-      <c r="AD38" s="18">
+      <c r="AD38" s="17">
         <f>AB35</f>
         <v>0.59557946837396036</v>
       </c>
-      <c r="AH38" s="17"/>
-      <c r="AI38" s="17"/>
-      <c r="AL38" s="34">
+      <c r="AH38" s="16"/>
+      <c r="AI38" s="16"/>
+      <c r="AL38" s="30">
         <f>AH35</f>
         <v>3</v>
       </c>
-      <c r="AM38" s="18">
+      <c r="AM38" s="17">
         <f>AK35</f>
         <v>-0.35597255211007783</v>
       </c>
     </row>
     <row r="39" spans="24:39" x14ac:dyDescent="0.25">
-      <c r="AC39" s="34">
+      <c r="AC39" s="30">
         <f>Y36</f>
         <v>4</v>
       </c>
-      <c r="AD39" s="18">
+      <c r="AD39" s="17">
         <f>AA36</f>
         <v>2.0938509024440652E-3</v>
       </c>
-      <c r="AL39" s="34">
+      <c r="AL39" s="30">
         <f>AH36</f>
         <v>4</v>
       </c>
-      <c r="AM39" s="18">
+      <c r="AM39" s="17">
         <f>AJ36</f>
         <v>5.1908974160972107E-2</v>
       </c>
     </row>
     <row r="40" spans="24:39" x14ac:dyDescent="0.25">
-      <c r="Y40" s="17"/>
-      <c r="Z40" s="17"/>
-      <c r="AC40" s="34">
+      <c r="Y40" s="16"/>
+      <c r="Z40" s="16"/>
+      <c r="AC40" s="30">
         <f>Y36</f>
         <v>4</v>
       </c>
-      <c r="AD40" s="18">
+      <c r="AD40" s="17">
         <f>AB36</f>
         <v>2.1736250964361186</v>
       </c>
-      <c r="AH40" s="17"/>
-      <c r="AI40" s="17"/>
-      <c r="AL40" s="34">
+      <c r="AH40" s="16"/>
+      <c r="AI40" s="16"/>
+      <c r="AL40" s="30">
         <f>AH36</f>
         <v>4</v>
       </c>
-      <c r="AM40" s="18">
+      <c r="AM40" s="17">
         <f>AK36</f>
         <v>3.9772269087838268</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L4" r:id="rId1" display="mAP@50"/>
-    <hyperlink ref="M4" r:id="rId2" display="mAP@50-95"/>
+    <hyperlink ref="L4" r:id="rId1" display="mAP@50" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="M4" r:id="rId2" display="mAP@50-95" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
@@ -14825,7 +14820,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:X54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14840,7 +14835,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
@@ -14852,65 +14847,65 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:24" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="O4" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="P4" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="15" t="s">
+      <c r="Q4" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="T4" s="15" t="s">
+      <c r="T4" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="U4" s="15" t="s">
+      <c r="U4" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="V4" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="W4" s="15" t="s">
+      <c r="W4" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="X4" s="15" t="s">
+      <c r="X4" s="14" t="s">
         <v>58</v>
       </c>
     </row>
@@ -14918,7 +14913,7 @@
       <c r="A5" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>45</v>
       </c>
       <c r="C5">
@@ -14930,16 +14925,16 @@
       <c r="E5">
         <v>446</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>0.59756100000000001</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>9.8989999999999995E-2</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <v>0.16984399999999999</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="K5" s="16" t="s">
         <v>45</v>
       </c>
       <c r="L5">
@@ -14951,30 +14946,30 @@
       <c r="N5">
         <v>446</v>
       </c>
-      <c r="O5" s="16">
+      <c r="O5" s="15">
         <v>0.59756100000000001</v>
       </c>
-      <c r="P5" s="16">
+      <c r="P5" s="15">
         <v>9.8989999999999995E-2</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="Q5" s="15">
         <v>0.16984399999999999</v>
       </c>
       <c r="T5" t="s">
         <v>85</v>
       </c>
-      <c r="U5" s="17" t="s">
+      <c r="U5" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="V5" s="18">
+      <c r="V5" s="17">
         <f>F8/IF(B8="S",$F$5,IF(B8="M",$F$6,$F$7))-1</f>
         <v>-0.23432586798669919</v>
       </c>
-      <c r="W5" s="18">
+      <c r="W5" s="17">
         <f>G8/IF(B8="S",$G$5,IF(B8="M",$G$6,$G$7))-1</f>
         <v>7.7959086776442064</v>
       </c>
-      <c r="X5" s="18">
+      <c r="X5" s="17">
         <f>H8/IF(B8="S",$H$5,IF(B8="M",$H$6,$H$7))-1</f>
         <v>2.5318350957349098</v>
       </c>
@@ -14983,7 +14978,7 @@
       <c r="A6" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>46</v>
       </c>
       <c r="C6">
@@ -14995,16 +14990,16 @@
       <c r="E6">
         <v>526</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="15">
         <v>0.87272700000000003</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="15">
         <v>8.3624000000000004E-2</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="15">
         <v>0.15262300000000001</v>
       </c>
-      <c r="K6" s="17" t="s">
+      <c r="K6" s="16" t="s">
         <v>46</v>
       </c>
       <c r="L6">
@@ -15016,30 +15011,30 @@
       <c r="N6">
         <v>526</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O6" s="15">
         <v>0.87272700000000003</v>
       </c>
-      <c r="P6" s="16">
+      <c r="P6" s="15">
         <v>8.3624000000000004E-2</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="Q6" s="15">
         <v>0.15262300000000001</v>
       </c>
       <c r="T6" t="s">
         <v>85</v>
       </c>
-      <c r="U6" s="17" t="s">
+      <c r="U6" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="V6" s="18">
+      <c r="V6" s="17">
         <f t="shared" ref="V6:V16" si="0">F9/IF(B9="S",$F$5,IF(B9="M",$F$6,$F$7))-1</f>
         <v>-0.17185901203927467</v>
       </c>
-      <c r="W6" s="18">
+      <c r="W6" s="17">
         <f t="shared" ref="W6:W16" si="1">G9/IF(B9="S",$G$5,IF(B9="M",$G$6,$G$7))-1</f>
         <v>8.6666268057017124</v>
       </c>
-      <c r="X6" s="18">
+      <c r="X6" s="17">
         <f t="shared" ref="X6:X16" si="2">H9/IF(B9="S",$H$5,IF(B9="M",$H$6,$H$7))-1</f>
         <v>4.0002817399736603</v>
       </c>
@@ -15048,7 +15043,7 @@
       <c r="A7" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>47</v>
       </c>
       <c r="C7">
@@ -15060,16 +15055,16 @@
       <c r="E7">
         <v>624</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="15">
         <v>0.77333300000000005</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="15">
         <v>8.5043999999999995E-2</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="15">
         <v>0.15323600000000001</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="16" t="s">
         <v>47</v>
       </c>
       <c r="L7">
@@ -15081,30 +15076,30 @@
       <c r="N7">
         <v>624</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O7" s="15">
         <v>0.77333300000000005</v>
       </c>
-      <c r="P7" s="16">
+      <c r="P7" s="15">
         <v>8.5043999999999995E-2</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="15">
         <v>0.15323600000000001</v>
       </c>
       <c r="T7" t="s">
         <v>85</v>
       </c>
-      <c r="U7" s="17" t="s">
+      <c r="U7" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="V7" s="18">
+      <c r="V7" s="17">
         <f t="shared" si="0"/>
         <v>-4.2309069960806078E-2</v>
       </c>
-      <c r="W7" s="18">
+      <c r="W7" s="17">
         <f t="shared" si="1"/>
         <v>6.4827618644466405</v>
       </c>
-      <c r="X7" s="18">
+      <c r="X7" s="17">
         <f t="shared" si="2"/>
         <v>3.4672466000156623</v>
       </c>
@@ -15113,7 +15108,7 @@
       <c r="A8" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>45</v>
       </c>
       <c r="C8">
@@ -15125,34 +15120,34 @@
       <c r="E8">
         <v>64</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>0.45753700000000003</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="15">
         <v>0.87070700000000001</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="15">
         <v>0.59986099999999998</v>
       </c>
-      <c r="L8" s="17"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
       <c r="T8" t="s">
         <v>74</v>
       </c>
-      <c r="U8" s="17" t="s">
+      <c r="U8" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="V8" s="18">
+      <c r="V8" s="17">
         <f t="shared" si="0"/>
         <v>8.775505764265068E-2</v>
       </c>
-      <c r="W8" s="18">
+      <c r="W8" s="17">
         <f t="shared" si="1"/>
         <v>1.6530558642287105</v>
       </c>
-      <c r="X8" s="18">
+      <c r="X8" s="17">
         <f t="shared" si="2"/>
         <v>1.2026153411365725</v>
       </c>
@@ -15161,7 +15156,7 @@
       <c r="A9" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>46</v>
       </c>
       <c r="C9">
@@ -15173,34 +15168,34 @@
       <c r="E9">
         <v>110</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>0.72274099999999997</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="15">
         <v>0.80836200000000002</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="15">
         <v>0.763158</v>
       </c>
-      <c r="L9" s="17"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
       <c r="T9" t="s">
         <v>74</v>
       </c>
-      <c r="U9" s="17" t="s">
+      <c r="U9" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="V9" s="18">
+      <c r="V9" s="17">
         <f t="shared" si="0"/>
         <v>-0.19064151790880768</v>
       </c>
-      <c r="W9" s="18">
+      <c r="W9" s="17">
         <f t="shared" si="1"/>
         <v>0.85415670142542788</v>
       </c>
-      <c r="X9" s="18">
+      <c r="X9" s="17">
         <f t="shared" si="2"/>
         <v>0.66610537075014897</v>
       </c>
@@ -15209,7 +15204,7 @@
       <c r="A10" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>47</v>
       </c>
       <c r="C10">
@@ -15221,34 +15216,34 @@
       <c r="E10">
         <v>248</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>0.74061399999999999</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="15">
         <v>0.63636400000000004</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="15">
         <v>0.68454300000000001</v>
       </c>
-      <c r="L10" s="17"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
       <c r="T10" t="s">
         <v>74</v>
       </c>
-      <c r="U10" s="17" t="s">
+      <c r="U10" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="V10" s="18">
+      <c r="V10" s="17">
         <f t="shared" si="0"/>
         <v>-0.35344799717586084</v>
       </c>
-      <c r="W10" s="18">
+      <c r="W10" s="17">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="X10" s="18">
+      <c r="X10" s="17">
         <f t="shared" si="2"/>
         <v>0.6564580124774857</v>
       </c>
@@ -15257,7 +15252,7 @@
       <c r="A11" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>45</v>
       </c>
       <c r="C11">
@@ -15269,34 +15264,34 @@
       <c r="E11">
         <v>365</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>0.65</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="15">
         <v>0.26262600000000003</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="15">
         <v>0.37410100000000002</v>
       </c>
-      <c r="L11" s="17"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
       <c r="T11" t="s">
         <v>50</v>
       </c>
-      <c r="U11" s="17" t="s">
+      <c r="U11" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="V11" s="18">
+      <c r="V11" s="17">
         <f t="shared" si="0"/>
         <v>0.30648084463343483</v>
       </c>
-      <c r="W11" s="18">
+      <c r="W11" s="17">
         <f t="shared" si="1"/>
         <v>0.81632488130114167</v>
       </c>
-      <c r="X11" s="18">
+      <c r="X11" s="17">
         <f t="shared" si="2"/>
         <v>0.7208850474553119</v>
       </c>
@@ -15305,7 +15300,7 @@
       <c r="A12" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>46</v>
       </c>
       <c r="C12">
@@ -15317,34 +15312,34 @@
       <c r="E12">
         <v>485</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>0.706349</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="15">
         <v>0.155052</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="15">
         <v>0.25428600000000001</v>
       </c>
-      <c r="L12" s="17"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
       <c r="T12" t="s">
         <v>50</v>
       </c>
-      <c r="U12" s="17" t="s">
+      <c r="U12" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="V12" s="18">
+      <c r="V12" s="17">
         <f t="shared" si="0"/>
         <v>-0.44098899197572661</v>
       </c>
-      <c r="W12" s="18">
+      <c r="W12" s="17">
         <f t="shared" si="1"/>
         <v>3.1874820625657705</v>
       </c>
-      <c r="X12" s="18">
+      <c r="X12" s="17">
         <f t="shared" si="2"/>
         <v>1.6713404925863076</v>
       </c>
@@ -15353,7 +15348,7 @@
       <c r="A13" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>47</v>
       </c>
       <c r="C13">
@@ -15365,34 +15360,34 @@
       <c r="E13">
         <v>566</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="15">
         <v>0.5</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="15">
         <v>0.17008799999999999</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="15">
         <v>0.25382900000000003</v>
       </c>
-      <c r="L13" s="17"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
       <c r="T13" t="s">
         <v>50</v>
       </c>
-      <c r="U13" s="17" t="s">
+      <c r="U13" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="V13" s="18">
+      <c r="V13" s="17">
         <f t="shared" si="0"/>
         <v>-0.52090884521932979</v>
       </c>
-      <c r="W13" s="18">
+      <c r="W13" s="17">
         <f t="shared" si="1"/>
         <v>2.7241427966699594</v>
       </c>
-      <c r="X13" s="18">
+      <c r="X13" s="17">
         <f t="shared" si="2"/>
         <v>1.2286016340807642</v>
       </c>
@@ -15401,7 +15396,7 @@
       <c r="A14" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="16" t="s">
         <v>45</v>
       </c>
       <c r="C14">
@@ -15413,34 +15408,34 @@
       <c r="E14">
         <v>406</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>0.78070200000000001</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <v>0.17979800000000001</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <v>0.29228199999999999</v>
       </c>
-      <c r="L14" s="17"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
       <c r="T14" t="s">
         <v>84</v>
       </c>
-      <c r="U14" s="17" t="s">
+      <c r="U14" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="V14" s="18">
+      <c r="V14" s="17">
         <f t="shared" si="0"/>
         <v>-5.0416610187077104E-2</v>
       </c>
-      <c r="W14" s="18">
+      <c r="W14" s="17">
         <f t="shared" si="1"/>
         <v>6.0408122032528544</v>
       </c>
-      <c r="X14" s="18">
+      <c r="X14" s="17">
         <f t="shared" si="2"/>
         <v>2.6831857469207039</v>
       </c>
@@ -15449,7 +15444,7 @@
       <c r="A15" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="16" t="s">
         <v>46</v>
       </c>
       <c r="C15">
@@ -15461,34 +15456,34 @@
       <c r="E15">
         <v>373</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="15">
         <v>0.48786400000000002</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="15">
         <v>0.35017399999999999</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="15">
         <v>0.40770800000000001</v>
       </c>
-      <c r="L15" s="17"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
       <c r="T15" t="s">
         <v>84</v>
       </c>
-      <c r="U15" s="17" t="s">
+      <c r="U15" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="V15" s="18">
+      <c r="V15" s="17">
         <f t="shared" si="0"/>
         <v>-0.1286438943678837</v>
       </c>
-      <c r="W15" s="18">
+      <c r="W15" s="17">
         <f t="shared" si="1"/>
         <v>7.3333014445613696</v>
       </c>
-      <c r="X15" s="18">
+      <c r="X15" s="17">
         <f t="shared" si="2"/>
         <v>3.7651599038152828</v>
       </c>
@@ -15497,7 +15492,7 @@
       <c r="A16" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>47</v>
       </c>
       <c r="C16">
@@ -15509,34 +15504,34 @@
       <c r="E16">
         <v>466</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>0.37049700000000002</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="15">
         <v>0.316716</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="15">
         <v>0.34150199999999997</v>
       </c>
-      <c r="L16" s="17"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
       <c r="T16" t="s">
         <v>84</v>
       </c>
-      <c r="U16" s="17" t="s">
+      <c r="U16" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="V16" s="18">
+      <c r="V16" s="17">
         <f t="shared" si="0"/>
         <v>-4.2144845752088766E-2</v>
       </c>
-      <c r="W16" s="18">
+      <c r="W16" s="17">
         <f t="shared" si="1"/>
         <v>6.5862024363858716</v>
       </c>
-      <c r="X16" s="18">
+      <c r="X16" s="17">
         <f t="shared" si="2"/>
         <v>3.5006069069931343</v>
       </c>
@@ -15545,7 +15540,7 @@
       <c r="A17" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>45</v>
       </c>
       <c r="C17">
@@ -15557,25 +15552,25 @@
       <c r="E17">
         <v>150</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="15">
         <v>0.56743399999999999</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="15">
         <v>0.69696999999999998</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="15">
         <v>0.62556699999999998</v>
       </c>
-      <c r="L17" s="17"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>46</v>
       </c>
       <c r="C18">
@@ -15587,25 +15582,25 @@
       <c r="E18">
         <v>174</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>0.76045600000000002</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="15">
         <v>0.69686400000000004</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="15">
         <v>0.72727299999999995</v>
       </c>
-      <c r="L18" s="17"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>47</v>
       </c>
       <c r="C19">
@@ -15617,36 +15612,36 @@
       <c r="E19">
         <v>242</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="15">
         <v>0.74074099999999998</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="15">
         <v>0.64516099999999998</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="15">
         <v>0.68965500000000002</v>
       </c>
-      <c r="L19" s="17"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="T19" s="15"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="15"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="15"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="U20" s="15" t="s">
+      <c r="U20" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="V20" s="15" t="s">
+      <c r="V20" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="W20" s="15" t="s">
+      <c r="W20" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="X20" s="15" t="s">
+      <c r="X20" s="14" t="s">
         <v>58</v>
       </c>
     </row>
@@ -15654,16 +15649,16 @@
       <c r="U21" t="s">
         <v>95</v>
       </c>
-      <c r="V21" s="32">
-        <f>ROUND(F8-IF(B8="S",$F$5,IF(B8="M",$F$6,$F$7)),2)</f>
+      <c r="V21" s="28">
+        <f t="shared" ref="V21:V32" si="3">ROUND(F8-IF(B8="S",$F$5,IF(B8="M",$F$6,$F$7)),2)</f>
         <v>-0.14000000000000001</v>
       </c>
-      <c r="W21" s="32">
-        <f>ROUND(G8-IF(B8="S",$G$5,IF(B8="M",$G$6,$G$7)),2)</f>
+      <c r="W21" s="28">
+        <f t="shared" ref="W21:W32" si="4">ROUND(G8-IF(B8="S",$G$5,IF(B8="M",$G$6,$G$7)),2)</f>
         <v>0.77</v>
       </c>
-      <c r="X21" s="32">
-        <f>ROUND(H8-IF(B8="S",$H$5,IF(B8="M",$H$6,$H$7)),2)</f>
+      <c r="X21" s="28">
+        <f t="shared" ref="X21:X32" si="5">ROUND(H8-IF(B8="S",$H$5,IF(B8="M",$H$6,$H$7)),2)</f>
         <v>0.43</v>
       </c>
     </row>
@@ -15671,16 +15666,16 @@
       <c r="U22" t="s">
         <v>96</v>
       </c>
-      <c r="V22" s="32">
-        <f>ROUND(F9-IF(B9="S",$F$5,IF(B9="M",$F$6,$F$7)),2)</f>
+      <c r="V22" s="28">
+        <f t="shared" si="3"/>
         <v>-0.15</v>
       </c>
-      <c r="W22" s="32">
-        <f>ROUND(G9-IF(B9="S",$G$5,IF(B9="M",$G$6,$G$7)),2)</f>
+      <c r="W22" s="28">
+        <f t="shared" si="4"/>
         <v>0.72</v>
       </c>
-      <c r="X22" s="32">
-        <f>ROUND(H9-IF(B9="S",$H$5,IF(B9="M",$H$6,$H$7)),2)</f>
+      <c r="X22" s="28">
+        <f t="shared" si="5"/>
         <v>0.61</v>
       </c>
     </row>
@@ -15688,16 +15683,16 @@
       <c r="U23" t="s">
         <v>97</v>
       </c>
-      <c r="V23" s="32">
-        <f>ROUND(F10-IF(B10="S",$F$5,IF(B10="M",$F$6,$F$7)),2)</f>
+      <c r="V23" s="28">
+        <f t="shared" si="3"/>
         <v>-0.03</v>
       </c>
-      <c r="W23" s="32">
-        <f>ROUND(G10-IF(B10="S",$G$5,IF(B10="M",$G$6,$G$7)),2)</f>
+      <c r="W23" s="28">
+        <f t="shared" si="4"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="X23" s="32">
-        <f>ROUND(H10-IF(B10="S",$H$5,IF(B10="M",$H$6,$H$7)),2)</f>
+      <c r="X23" s="28">
+        <f t="shared" si="5"/>
         <v>0.53</v>
       </c>
     </row>
@@ -15705,48 +15700,48 @@
       <c r="U24" t="s">
         <v>87</v>
       </c>
-      <c r="V24" s="32">
-        <f>ROUND(F11-IF(B11="S",$F$5,IF(B11="M",$F$6,$F$7)),2)</f>
+      <c r="V24" s="28">
+        <f t="shared" si="3"/>
         <v>0.05</v>
       </c>
-      <c r="W24" s="32">
-        <f>ROUND(G11-IF(B11="S",$G$5,IF(B11="M",$G$6,$G$7)),2)</f>
+      <c r="W24" s="28">
+        <f t="shared" si="4"/>
         <v>0.16</v>
       </c>
-      <c r="X24" s="32">
-        <f>ROUND(H11-IF(B11="S",$H$5,IF(B11="M",$H$6,$H$7)),2)</f>
+      <c r="X24" s="28">
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="14" t="s">
         <v>58</v>
       </c>
       <c r="U25" t="s">
         <v>88</v>
       </c>
-      <c r="V25" s="32">
-        <f>ROUND(F12-IF(B12="S",$F$5,IF(B12="M",$F$6,$F$7)),2)</f>
+      <c r="V25" s="28">
+        <f t="shared" si="3"/>
         <v>-0.17</v>
       </c>
-      <c r="W25" s="32">
-        <f>ROUND(G12-IF(B12="S",$G$5,IF(B12="M",$G$6,$G$7)),2)</f>
+      <c r="W25" s="28">
+        <f t="shared" si="4"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="X25" s="32">
-        <f>ROUND(H12-IF(B12="S",$H$5,IF(B12="M",$H$6,$H$7)),2)</f>
+      <c r="X25" s="28">
+        <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
     </row>
@@ -15754,7 +15749,7 @@
       <c r="A26" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="16" t="s">
         <v>45</v>
       </c>
       <c r="C26">
@@ -15769,16 +15764,16 @@
       <c r="U26" t="s">
         <v>86</v>
       </c>
-      <c r="V26" s="32">
-        <f>ROUND(F13-IF(B13="S",$F$5,IF(B13="M",$F$6,$F$7)),2)</f>
+      <c r="V26" s="28">
+        <f t="shared" si="3"/>
         <v>-0.27</v>
       </c>
-      <c r="W26" s="32">
-        <f>ROUND(G13-IF(B13="S",$G$5,IF(B13="M",$G$6,$G$7)),2)</f>
+      <c r="W26" s="28">
+        <f t="shared" si="4"/>
         <v>0.09</v>
       </c>
-      <c r="X26" s="32">
-        <f>ROUND(H13-IF(B13="S",$H$5,IF(B13="M",$H$6,$H$7)),2)</f>
+      <c r="X26" s="28">
+        <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
     </row>
@@ -15786,7 +15781,7 @@
       <c r="A27" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="16" t="s">
         <v>46</v>
       </c>
       <c r="C27">
@@ -15798,20 +15793,20 @@
       <c r="E27">
         <v>0.61</v>
       </c>
-      <c r="I27" s="13"/>
+      <c r="I27" s="12"/>
       <c r="U27" t="s">
         <v>89</v>
       </c>
-      <c r="V27" s="32">
-        <f>ROUND(F14-IF(B14="S",$F$5,IF(B14="M",$F$6,$F$7)),2)</f>
+      <c r="V27" s="28">
+        <f t="shared" si="3"/>
         <v>0.18</v>
       </c>
-      <c r="W27" s="32">
-        <f>ROUND(G14-IF(B14="S",$G$5,IF(B14="M",$G$6,$G$7)),2)</f>
+      <c r="W27" s="28">
+        <f t="shared" si="4"/>
         <v>0.08</v>
       </c>
-      <c r="X27" s="32">
-        <f>ROUND(H14-IF(B14="S",$H$5,IF(B14="M",$H$6,$H$7)),2)</f>
+      <c r="X27" s="28">
+        <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
     </row>
@@ -15819,7 +15814,7 @@
       <c r="A28" t="s">
         <v>85</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="16" t="s">
         <v>47</v>
       </c>
       <c r="C28">
@@ -15834,16 +15829,16 @@
       <c r="U28" t="s">
         <v>90</v>
       </c>
-      <c r="V28" s="32">
-        <f>ROUND(F15-IF(B15="S",$F$5,IF(B15="M",$F$6,$F$7)),2)</f>
+      <c r="V28" s="28">
+        <f t="shared" si="3"/>
         <v>-0.38</v>
       </c>
-      <c r="W28" s="32">
-        <f>ROUND(G15-IF(B15="S",$G$5,IF(B15="M",$G$6,$G$7)),2)</f>
+      <c r="W28" s="28">
+        <f t="shared" si="4"/>
         <v>0.27</v>
       </c>
-      <c r="X28" s="32">
-        <f>ROUND(H15-IF(B15="S",$H$5,IF(B15="M",$H$6,$H$7)),2)</f>
+      <c r="X28" s="28">
+        <f t="shared" si="5"/>
         <v>0.26</v>
       </c>
     </row>
@@ -15851,7 +15846,7 @@
       <c r="A29" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="16" t="s">
         <v>45</v>
       </c>
       <c r="C29">
@@ -15866,16 +15861,16 @@
       <c r="U29" t="s">
         <v>91</v>
       </c>
-      <c r="V29" s="32">
-        <f>ROUND(F16-IF(B16="S",$F$5,IF(B16="M",$F$6,$F$7)),2)</f>
+      <c r="V29" s="28">
+        <f t="shared" si="3"/>
         <v>-0.4</v>
       </c>
-      <c r="W29" s="32">
-        <f>ROUND(G16-IF(B16="S",$G$5,IF(B16="M",$G$6,$G$7)),2)</f>
+      <c r="W29" s="28">
+        <f t="shared" si="4"/>
         <v>0.23</v>
       </c>
-      <c r="X29" s="32">
-        <f>ROUND(H16-IF(B16="S",$H$5,IF(B16="M",$H$6,$H$7)),2)</f>
+      <c r="X29" s="28">
+        <f t="shared" si="5"/>
         <v>0.19</v>
       </c>
     </row>
@@ -15883,7 +15878,7 @@
       <c r="A30" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="16" t="s">
         <v>46</v>
       </c>
       <c r="C30">
@@ -15901,16 +15896,16 @@
       <c r="U30" t="s">
         <v>92</v>
       </c>
-      <c r="V30" s="32">
-        <f>ROUND(F17-IF(B17="S",$F$5,IF(B17="M",$F$6,$F$7)),2)</f>
+      <c r="V30" s="28">
+        <f t="shared" si="3"/>
         <v>-0.03</v>
       </c>
-      <c r="W30" s="32">
-        <f>ROUND(G17-IF(B17="S",$G$5,IF(B17="M",$G$6,$G$7)),2)</f>
+      <c r="W30" s="28">
+        <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
-      <c r="X30" s="32">
-        <f>ROUND(H17-IF(B17="S",$H$5,IF(B17="M",$H$6,$H$7)),2)</f>
+      <c r="X30" s="28">
+        <f t="shared" si="5"/>
         <v>0.46</v>
       </c>
     </row>
@@ -15918,7 +15913,7 @@
       <c r="A31" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="16" t="s">
         <v>47</v>
       </c>
       <c r="C31">
@@ -15933,16 +15928,16 @@
       <c r="U31" t="s">
         <v>93</v>
       </c>
-      <c r="V31" s="32">
-        <f>ROUND(F18-IF(B18="S",$F$5,IF(B18="M",$F$6,$F$7)),2)</f>
+      <c r="V31" s="28">
+        <f t="shared" si="3"/>
         <v>-0.11</v>
       </c>
-      <c r="W31" s="32">
-        <f>ROUND(G18-IF(B18="S",$G$5,IF(B18="M",$G$6,$G$7)),2)</f>
+      <c r="W31" s="28">
+        <f t="shared" si="4"/>
         <v>0.61</v>
       </c>
-      <c r="X31" s="32">
-        <f>ROUND(H18-IF(B18="S",$H$5,IF(B18="M",$H$6,$H$7)),2)</f>
+      <c r="X31" s="28">
+        <f t="shared" si="5"/>
         <v>0.56999999999999995</v>
       </c>
     </row>
@@ -15950,7 +15945,7 @@
       <c r="A32" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="16" t="s">
         <v>45</v>
       </c>
       <c r="C32">
@@ -15965,16 +15960,16 @@
       <c r="U32" t="s">
         <v>94</v>
       </c>
-      <c r="V32" s="32">
-        <f>ROUND(F19-IF(B19="S",$F$5,IF(B19="M",$F$6,$F$7)),2)</f>
+      <c r="V32" s="28">
+        <f t="shared" si="3"/>
         <v>-0.03</v>
       </c>
-      <c r="W32" s="32">
-        <f>ROUND(G19-IF(B19="S",$G$5,IF(B19="M",$G$6,$G$7)),2)</f>
+      <c r="W32" s="28">
+        <f t="shared" si="4"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="X32" s="32">
-        <f>ROUND(H19-IF(B19="S",$H$5,IF(B19="M",$H$6,$H$7)),2)</f>
+      <c r="X32" s="28">
+        <f t="shared" si="5"/>
         <v>0.54</v>
       </c>
     </row>
@@ -15982,7 +15977,7 @@
       <c r="A33" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="16" t="s">
         <v>46</v>
       </c>
       <c r="C33">
@@ -15999,7 +15994,7 @@
       <c r="A34" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="16" t="s">
         <v>47</v>
       </c>
       <c r="C34">
@@ -16016,7 +16011,7 @@
       <c r="A35" t="s">
         <v>84</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="16" t="s">
         <v>45</v>
       </c>
       <c r="C35">
@@ -16033,7 +16028,7 @@
       <c r="A36" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="16" t="s">
         <v>46</v>
       </c>
       <c r="C36">
@@ -16045,16 +16040,16 @@
       <c r="E36">
         <v>0.56999999999999995</v>
       </c>
-      <c r="T36" s="15" t="s">
+      <c r="T36" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="U36" s="15" t="s">
+      <c r="U36" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="V36" s="15" t="s">
+      <c r="V36" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="W36" s="15" t="s">
+      <c r="W36" s="14" t="s">
         <v>78</v>
       </c>
     </row>
@@ -16062,7 +16057,7 @@
       <c r="A37" t="s">
         <v>84</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="16" t="s">
         <v>47</v>
       </c>
       <c r="C37">
@@ -16145,16 +16140,16 @@
       <c r="V41" s="3"/>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="T43" s="15" t="s">
+      <c r="T43" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="U43" s="15" t="s">
+      <c r="U43" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="V43" s="15" t="s">
+      <c r="V43" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="W43" s="15" t="s">
+      <c r="W43" s="14" t="s">
         <v>78</v>
       </c>
     </row>
@@ -16227,16 +16222,16 @@
       </c>
     </row>
     <row r="50" spans="20:23" x14ac:dyDescent="0.25">
-      <c r="T50" s="15" t="s">
+      <c r="T50" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="U50" s="15" t="s">
+      <c r="U50" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="V50" s="15" t="s">
+      <c r="V50" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="W50" s="15" t="s">
+      <c r="W50" s="14" t="s">
         <v>78</v>
       </c>
     </row>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Projects\NAC-YOLO-Training\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61210C14-123B-4B72-8278-96844641831B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Wybrane obserwacje LROC NAC" sheetId="1" r:id="rId1"/>
@@ -56,8 +55,8 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="creater_sizes" type="6" refreshedVersion="6" background="1" saveData="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="creater_sizes" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -71,7 +70,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="2" xr16:uid="{00000000-0015-0000-FFFF-FFFF01000000}" name="creater_sizes1" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="2" name="creater_sizes1" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_downsampling_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -85,7 +84,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="3" xr16:uid="{00000000-0015-0000-FFFF-FFFF02000000}" name="creater_sizes11" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="3" name="creater_sizes11" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_downsampling_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -99,7 +98,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="4" xr16:uid="{00000000-0015-0000-FFFF-FFFF03000000}" name="creater_sizes12" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="4" name="creater_sizes12" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_downsampling_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -113,7 +112,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="5" xr16:uid="{00000000-0015-0000-FFFF-FFFF04000000}" name="creater_sizes121" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="5" name="creater_sizes121" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_downsampling_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -127,7 +126,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="6" xr16:uid="{00000000-0015-0000-FFFF-FFFF05000000}" name="creater_sizes1211" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="6" name="creater_sizes1211" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_downsampling_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -141,7 +140,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="7" xr16:uid="{00000000-0015-0000-FFFF-FFFF06000000}" name="creater_sizes1212" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="7" name="creater_sizes1212" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_downsampling_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -155,7 +154,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="8" xr16:uid="{00000000-0015-0000-FFFF-FFFF07000000}" name="creater_sizes2" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="8" name="creater_sizes2" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_blur_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -169,7 +168,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="9" xr16:uid="{00000000-0015-0000-FFFF-FFFF08000000}" name="creater_sizes21" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="9" name="creater_sizes21" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_blur_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -183,7 +182,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="10" xr16:uid="{00000000-0015-0000-FFFF-FFFF09000000}" name="creater_sizes22" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="10" name="creater_sizes22" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_blur_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -197,7 +196,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="11" xr16:uid="{00000000-0015-0000-FFFF-FFFF0A000000}" name="creater_sizes221" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="11" name="creater_sizes221" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_blur_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -211,7 +210,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="12" xr16:uid="{00000000-0015-0000-FFFF-FFFF0B000000}" name="creater_sizes2211" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="12" name="creater_sizes2211" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_blur_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -225,7 +224,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="13" xr16:uid="{00000000-0015-0000-FFFF-FFFF0C000000}" name="creater_sizes2212" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="13" name="creater_sizes2212" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_blur_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -239,7 +238,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="14" xr16:uid="{00000000-0015-0000-FFFF-FFFF0D000000}" name="creater_sizes3" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="14" name="creater_sizes3" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_summation_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -253,7 +252,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="15" xr16:uid="{00000000-0015-0000-FFFF-FFFF0E000000}" name="creater_sizes31" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="15" name="creater_sizes31" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_summation_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -267,7 +266,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="16" xr16:uid="{00000000-0015-0000-FFFF-FFFF0F000000}" name="creater_sizes32" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="16" name="creater_sizes32" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_summation_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -281,7 +280,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="17" xr16:uid="{00000000-0015-0000-FFFF-FFFF10000000}" name="creater_sizes321" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="17" name="creater_sizes321" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_summation_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -295,7 +294,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="18" xr16:uid="{00000000-0015-0000-FFFF-FFFF11000000}" name="creater_sizes3211" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="18" name="creater_sizes3211" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_summation_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -309,7 +308,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="19" xr16:uid="{00000000-0015-0000-FFFF-FFFF12000000}" name="creater_sizes3212" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="19" name="creater_sizes3212" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_summation_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -323,7 +322,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="20" xr16:uid="{00000000-0015-0000-FFFF-FFFF13000000}" name="creater_sizes4" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="20" name="creater_sizes4" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_all_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -337,7 +336,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="21" xr16:uid="{00000000-0015-0000-FFFF-FFFF14000000}" name="creater_sizes41" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="21" name="creater_sizes41" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_all_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -351,7 +350,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="22" xr16:uid="{00000000-0015-0000-FFFF-FFFF15000000}" name="creater_sizes42" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="22" name="creater_sizes42" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_all_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -365,7 +364,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="23" xr16:uid="{00000000-0015-0000-FFFF-FFFF16000000}" name="creater_sizes421" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="23" name="creater_sizes421" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_all_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -379,7 +378,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="24" xr16:uid="{00000000-0015-0000-FFFF-FFFF17000000}" name="creater_sizes4211" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="24" name="creater_sizes4211" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_all_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -393,7 +392,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="25" xr16:uid="{00000000-0015-0000-FFFF-FFFF18000000}" name="creater_sizes4212" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="25" name="creater_sizes4212" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_all_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -407,7 +406,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="26" xr16:uid="{00000000-0015-0000-FFFF-FFFF19000000}" name="creater_sizes5" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="26" name="creater_sizes5" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -421,7 +420,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="27" xr16:uid="{00000000-0015-0000-FFFF-FFFF1A000000}" name="creater_sizes6" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="27" name="creater_sizes6" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -435,7 +434,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="28" xr16:uid="{00000000-0015-0000-FFFF-FFFF1B000000}" name="creater_sizes61" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="28" name="creater_sizes61" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -449,7 +448,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="29" xr16:uid="{00000000-0015-0000-FFFF-FFFF1C000000}" name="creater_sizes611" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="29" name="creater_sizes611" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -463,7 +462,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="30" xr16:uid="{00000000-0015-0000-FFFF-FFFF1D000000}" name="creater_sizes612" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="30" name="creater_sizes612" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="852" sourceFile="E:\WSB\Praca_Magisterska_2\Skrypty\NAC YOLO Training\runs\detect\val\300m_with_test_tuned_LQ\creater_sizes.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="8">
         <textField/>
@@ -780,7 +779,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -854,27 +853,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -917,10 +901,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -948,15 +928,19 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -1498,17 +1482,18 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{29F527A0-FEF9-4233-BD69-04B11D49F338}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{10F14B13-05E3-498A-88C3-F4E0C2AF2D4B}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1521,6 +1506,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -1532,17 +1518,18 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{95AC7FF8-AE0D-4C13-AF69-DD828FBC223F}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{B3E79FB8-A1F3-47C6-892D-539961E488AF}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1555,6 +1542,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -1566,17 +1554,18 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0BA6E71E-F51E-4669-A090-4CB09C2A7F4F}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{4C145976-BFCD-4A90-AB3C-DECF41ED00BB}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1589,6 +1578,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -1600,17 +1590,18 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C591520D-CAB9-438B-872D-278667A25597}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{2442C2A7-1355-4BD2-8C6A-109833ADD244}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1623,6 +1614,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -1640,9 +1632,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1653,9 +1643,9 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -1671,6 +1661,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showDataLabelsRange val="1"/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
@@ -1802,9 +1793,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1850,9 +1841,9 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -1871,6 +1862,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1891,9 +1883,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1929,9 +1921,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1965,9 +1957,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1994,6 +1986,7 @@
         <c:idx val="6"/>
         <c:delete val="1"/>
       </c:legendEntry>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2014,9 +2007,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -2047,7 +2040,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -2500,17 +2496,18 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{072E9790-9A52-46A1-A84E-0538EC41434E}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{B11D1988-BC73-435C-8AA1-9D910DDDAA05}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2523,6 +2520,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -2534,17 +2532,18 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6BEC6EC6-3A90-43B6-8355-C275888A49DA}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{3B71BB64-CEDB-4AE4-AD30-A5289FD96487}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2557,6 +2556,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -2568,17 +2568,18 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F4ECD5E9-3ADA-490C-BABC-DEA5E60BA5D0}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{74B780B1-EDB8-4E7E-A053-FF2EAF130F67}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2591,6 +2592,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -2602,17 +2604,18 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3FF86C36-D657-4726-AC2A-12AB9183B334}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{269431AB-9F09-414F-8E3F-6706BCFABBC1}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2625,6 +2628,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -2642,9 +2646,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -2655,9 +2657,9 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -2673,6 +2675,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showDataLabelsRange val="1"/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
@@ -2804,9 +2807,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -2852,37 +2855,28 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="pl-PL"/>
-                  <a:t>Zmiana czułości </a:t>
+                  <a:t>Zmiana czułości (</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="pl-PL" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:effectLst/>
-                  </a:rPr>
-                  <a:t>(</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="el-GR" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:effectLst/>
-                  </a:rPr>
+                  <a:rPr lang="el-GR"/>
                   <a:t>Δ</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="pl-PL" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:effectLst/>
-                  </a:rPr>
+                  <a:rPr lang="pl-PL"/>
                   <a:t>)</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2903,9 +2897,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -2941,9 +2935,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -2977,9 +2971,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -3006,6 +3000,7 @@
         <c:idx val="6"/>
         <c:delete val="1"/>
       </c:legendEntry>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3026,9 +3021,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -3059,7 +3054,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -3510,17 +3508,18 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E321D94E-977C-4FD1-A355-0C664551D6BB}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{577DA6AC-5AE2-494C-9CC3-24F2C1632699}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3533,6 +3532,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -3544,17 +3544,18 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6CC3E4F4-153D-4E6E-90A7-67460565A01F}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{E94CB5A8-C31E-4784-8916-3306CF4D223E}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3567,6 +3568,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -3578,17 +3580,18 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A1FEFC66-42DC-4479-8FF7-49C3ACDC6ADF}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{73D363C1-96E5-4E08-AC86-CDB5F32B1545}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3601,6 +3604,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -3612,17 +3616,18 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C9F71987-2566-40EB-A360-2B351E7EB367}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{BA63CBAF-428E-4F8B-8977-9200C6E867FB}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3635,6 +3640,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -3652,9 +3658,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -3665,9 +3669,9 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -3683,6 +3687,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showDataLabelsRange val="1"/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
@@ -3814,9 +3819,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -3862,37 +3867,28 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="pl-PL"/>
-                  <a:t>Zmiana mAP50 </a:t>
+                  <a:t>Zmiana mAP50 (</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="pl-PL" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:effectLst/>
-                  </a:rPr>
-                  <a:t>(</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="el-GR" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:effectLst/>
-                  </a:rPr>
+                  <a:rPr lang="el-GR"/>
                   <a:t>Δ</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="pl-PL" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:effectLst/>
-                  </a:rPr>
+                  <a:rPr lang="pl-PL"/>
                   <a:t>)</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3913,9 +3909,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -3951,9 +3947,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -3987,9 +3983,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4016,6 +4012,7 @@
         <c:idx val="6"/>
         <c:delete val="1"/>
       </c:legendEntry>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4036,9 +4033,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -4069,7 +4066,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -4522,17 +4522,18 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{06868FF4-B6B7-445D-AAB6-B136DDB2A802}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{B483BC3C-944B-4B15-8EE0-EFE559056D7B}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4545,6 +4546,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -4556,17 +4558,18 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F81D1158-7900-47D1-956B-AB0E205CEF0E}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{E916D207-3408-487F-943E-511880BB242A}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4579,6 +4582,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -4590,17 +4594,18 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D9B3C41D-0413-4ABA-98A0-D1A6FCA80F8B}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{9C79E189-B50E-447E-8F75-A98446EB87AB}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4613,6 +4618,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -4624,17 +4630,18 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
+              <c:layout/>
               <c:tx>
                 <c:rich>
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{581D2F6B-B3CF-4B83-98B2-D4D65FD05C5E}" type="CELLRANGE">
-                      <a:rPr lang="pl-PL"/>
+                    <a:fld id="{0B9534F4-2A9B-425D-8B20-2F827BC03280}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="pl-PL"/>
+                    <a:endParaRPr lang="en-US"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4647,6 +4654,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
@@ -4664,9 +4672,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -4677,9 +4683,9 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -4695,6 +4701,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showDataLabelsRange val="1"/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
@@ -4826,9 +4833,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4874,37 +4881,27 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="pl-PL"/>
-                  <a:t>Zmiana mAP50-95 </a:t>
+                  <a:t>Zmiana mAP50-95 (</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="pl-PL" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:effectLst/>
-                  </a:rPr>
-                  <a:t>(</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="el-GR" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:effectLst/>
-                  </a:rPr>
+                  <a:rPr lang="el-GR"/>
                   <a:t>Δ</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="pl-PL" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:effectLst/>
-                  </a:rPr>
+                  <a:rPr lang="pl-PL"/>
                   <a:t>)</a:t>
                 </a:r>
-                <a:endParaRPr lang="pl-PL"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -4925,12 +4922,12 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="pl-PL"/>
+              <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -4963,9 +4960,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4999,9 +4996,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -5028,6 +5025,7 @@
         <c:idx val="6"/>
         <c:delete val="1"/>
       </c:legendEntry>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5048,9 +5046,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -5081,7 +5079,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -5407,9 +5408,9 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -5420,6 +5421,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -5440,9 +5442,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -5478,9 +5480,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -5528,23 +5530,24 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:rPr lang="en-US"/>
                   <a:t>Zmiana precyzji (</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="el-GR" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:rPr lang="el-GR"/>
                   <a:t>Δ)</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -5565,9 +5568,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -5597,9 +5600,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -5619,6 +5622,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5639,9 +5643,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -5673,7 +5677,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -5998,21 +6005,20 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pl-PL" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:effectLst/>
-                  </a:rPr>
+                  <a:rPr lang="pl-PL"/>
                   <a:t>Scenariusz</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -6033,9 +6039,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -6071,9 +6077,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -6121,31 +6127,32 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:rPr lang="en-US"/>
                   <a:t>Zmiana </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="pl-PL" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:rPr lang="pl-PL"/>
                   <a:t>czułości</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:rPr lang="en-US"/>
                   <a:t> (</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="el-GR" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:rPr lang="el-GR"/>
                   <a:t>Δ)</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -6166,9 +6173,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -6198,9 +6205,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -6220,6 +6227,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6240,9 +6248,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -6273,7 +6281,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -6675,9 +6686,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -6725,31 +6736,32 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:rPr lang="en-US"/>
                   <a:t>Zmiana </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="pl-PL" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:rPr lang="pl-PL"/>
                   <a:t>F1</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:rPr lang="en-US"/>
                   <a:t> (</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="el-GR" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:rPr lang="el-GR"/>
                   <a:t>Δ)</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -6770,9 +6782,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -6802,9 +6814,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -6824,6 +6836,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6844,9 +6857,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -6877,7 +6890,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -7197,9 +7213,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -7249,23 +7265,20 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="pl-PL"/>
-                  <a:t>Zmiana metryk względem</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="pl-PL" baseline="0"/>
-                  <a:t> scenariusza bazowego</a:t>
+                  <a:t>Zmiana metryk względem scenariusza bazowego</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -7286,9 +7299,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -7318,9 +7331,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -7340,6 +7353,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7360,9 +7374,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -7393,7 +7407,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -12467,63 +12484,63 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes" connectionId="1" xr16:uid="{00000000-0016-0000-0300-00000E000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_11" connectionId="28" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_11" connectionId="28" xr16:uid="{00000000-0016-0000-0300-000005000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_12" connectionId="5" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_9" connectionId="27" xr16:uid="{00000000-0016-0000-0300-000004000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_5" connectionId="22" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_6" connectionId="16" xr16:uid="{00000000-0016-0000-0300-000003000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_4" connectionId="20" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_12" connectionId="5" xr16:uid="{00000000-0016-0000-0300-000002000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_10" connectionId="23" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_7" connectionId="10" xr16:uid="{00000000-0016-0000-0300-000001000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_7" connectionId="10" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_13" connectionId="11" xr16:uid="{00000000-0016-0000-0300-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_2" connectionId="8" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_1" connectionId="2" xr16:uid="{00000000-0016-0000-0300-00000D000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_14" connectionId="17" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_4" connectionId="20" xr16:uid="{00000000-0016-0000-0300-00000C000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_13" connectionId="11" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_2" connectionId="8" xr16:uid="{00000000-0016-0000-0300-00000B000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_14" connectionId="17" xr16:uid="{00000000-0016-0000-0300-00000A000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_9" connectionId="27" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_8" connectionId="4" xr16:uid="{00000000-0016-0000-0300-000009000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_8" connectionId="4" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_3" connectionId="14" xr16:uid="{00000000-0016-0000-0300-000008000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_1" connectionId="2" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_5" connectionId="22" xr16:uid="{00000000-0016-0000-0300-000007000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_6" connectionId="16" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="creater_sizes_10" connectionId="23" xr16:uid="{00000000-0016-0000-0300-000006000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="creater_sizes_3" connectionId="14" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12788,7 +12805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12799,7 +12816,7 @@
     <col min="5" max="5" width="10.7109375" style="16" customWidth="1"/>
     <col min="6" max="6" width="10.28515625" style="16" customWidth="1"/>
     <col min="7" max="7" width="10.140625" style="16" customWidth="1"/>
-    <col min="8" max="8" width="14" style="20" customWidth="1"/>
+    <col min="8" max="8" width="14" style="18" customWidth="1"/>
     <col min="9" max="9" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12838,25 +12855,25 @@
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="20" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="19">
         <v>0.59587928539432899</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="20">
         <v>66.88</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="19">
         <v>1.1399999999999999</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="20">
         <v>65.87</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="21" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12864,25 +12881,25 @@
       <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="19">
         <v>0.58256255764199005</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="20">
         <v>65.09</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="19">
         <v>1.7</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="20">
         <v>66.61</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="21" t="s">
         <v>66</v>
       </c>
     </row>
@@ -12890,25 +12907,25 @@
       <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="19">
         <v>0.59140474594205605</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="22">
         <v>64.94</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="19">
         <v>1.1399999999999999</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="20">
         <v>63.95</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="21" t="s">
         <v>67</v>
       </c>
     </row>
@@ -12916,25 +12933,25 @@
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="20" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="19">
         <v>0.58876450802762803</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="20">
         <v>62.88</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="19">
         <v>1.7</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="20">
         <v>64.42</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="21" t="s">
         <v>68</v>
       </c>
     </row>
@@ -12942,25 +12959,25 @@
       <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="20" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="19">
         <v>0.49227418493164998</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="20">
         <v>64.34</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="19">
         <v>1.1399999999999999</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="20">
         <v>63.27</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="21" t="s">
         <v>69</v>
       </c>
     </row>
@@ -12968,25 +12985,25 @@
       <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="20" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="19">
         <v>0.49439722050231499</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="20">
         <v>64.91</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="19">
         <v>1.69</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="20">
         <v>66.45</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="23" t="s">
         <v>70</v>
       </c>
     </row>
@@ -12994,25 +13011,25 @@
       <c r="A10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="20" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="19">
         <v>0.49933420700105502</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="20">
         <v>65.180000000000007</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="19">
         <v>1.1399999999999999</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="20">
         <v>64.11</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="23" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13020,25 +13037,25 @@
       <c r="A11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="19">
         <v>2.18856679415771</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="20">
         <v>71.08</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="19">
         <v>1.74</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="20">
         <v>72.78</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="23" t="s">
         <v>71</v>
       </c>
     </row>
@@ -13046,25 +13063,25 @@
       <c r="A12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="24">
         <v>2.1245861832302002</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="20">
         <v>71.47</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="19">
         <v>1.18</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="22">
         <v>70.34</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -13072,99 +13089,99 @@
       <c r="A13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="19">
         <v>2.1095564090528698</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="20">
         <v>70.81</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="19">
         <v>1.74</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="20">
         <v>72.52</v>
       </c>
-      <c r="H13" s="25" t="s">
+      <c r="H13" s="23" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
     </row>
     <row r="24" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13172,7 +13189,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13506,7 +13523,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AM40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13550,19 +13567,19 @@
       <c r="F4" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="18" t="s">
+      <c r="M4" s="29" t="s">
         <v>61</v>
       </c>
       <c r="P4" s="14" t="s">
@@ -13645,22 +13662,22 @@
       <c r="F5" s="15">
         <v>0.50433843829828395</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="31">
         <f>ROUND(0.759957994041264,3)</f>
         <v>0.76</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="31">
         <f>ROUND(0.759036144578313,3)</f>
         <v>0.75900000000000001</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="31">
         <f>ROUND(0.797625837411973,3)</f>
         <v>0.79800000000000004</v>
       </c>
-      <c r="M5" s="19">
+      <c r="M5" s="31">
         <f>ROUND(0.504338438298284,3)</f>
         <v>0.504</v>
       </c>
@@ -13692,7 +13709,7 @@
       <c r="Y5" s="16">
         <v>1</v>
       </c>
-      <c r="Z5" s="31">
+      <c r="Z5" s="28">
         <f>MIN($AA$5:$AB$8)-1%</f>
         <v>-0.28592643218061181</v>
       </c>
@@ -13702,7 +13719,7 @@
       <c r="AB5" s="17">
         <v>0.24831661785313733</v>
       </c>
-      <c r="AC5" s="30">
+      <c r="AC5" s="27">
         <f>Y5</f>
         <v>1</v>
       </c>
@@ -13716,7 +13733,7 @@
       <c r="AH5" s="16">
         <v>1</v>
       </c>
-      <c r="AI5" s="31">
+      <c r="AI5" s="28">
         <f>MIN($AJ$5:$AK$8)-31%</f>
         <v>-0.3849286187770114</v>
       </c>
@@ -13726,7 +13743,7 @@
       <c r="AK5" s="17">
         <v>1.899023224865569</v>
       </c>
-      <c r="AL5" s="30">
+      <c r="AL5" s="27">
         <f>AH5</f>
         <v>1</v>
       </c>
@@ -13754,22 +13771,22 @@
       <c r="F6" s="15">
         <v>8.1417102195645005E-2</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="31">
         <f>ROUND(0.546123673366799,3)</f>
         <v>0.54600000000000004</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="31">
         <f>ROUND(0.228440890919474,3)</f>
         <v>0.22800000000000001</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="31">
         <f>ROUND(0.260296669760787,3)</f>
         <v>0.26</v>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="31">
         <f>ROUND(0.081417102195645,3)</f>
         <v>8.1000000000000003E-2</v>
       </c>
@@ -13801,7 +13818,7 @@
       <c r="Y6" s="16">
         <v>2</v>
       </c>
-      <c r="Z6" s="31">
+      <c r="Z6" s="28">
         <f t="shared" ref="Z6:Z8" si="0">MIN($AA$5:$AB$8)-1%</f>
         <v>-0.28592643218061181</v>
       </c>
@@ -13811,7 +13828,7 @@
       <c r="AB6" s="17">
         <v>-0.1997633493290239</v>
       </c>
-      <c r="AC6" s="30">
+      <c r="AC6" s="27">
         <f>Y5</f>
         <v>1</v>
       </c>
@@ -13825,7 +13842,7 @@
       <c r="AH6" s="16">
         <v>2</v>
       </c>
-      <c r="AI6" s="31">
+      <c r="AI6" s="28">
         <f t="shared" ref="AI6:AI8" si="1">MIN($AJ$5:$AK$8)-31%</f>
         <v>-0.3849286187770114</v>
       </c>
@@ -13835,7 +13852,7 @@
       <c r="AK6" s="17">
         <v>0.15809703700931527</v>
       </c>
-      <c r="AL6" s="30">
+      <c r="AL6" s="27">
         <f>AH5</f>
         <v>1</v>
       </c>
@@ -13891,7 +13908,7 @@
       <c r="Y7" s="16">
         <v>3</v>
       </c>
-      <c r="Z7" s="31">
+      <c r="Z7" s="28">
         <f t="shared" si="0"/>
         <v>-0.28592643218061181</v>
       </c>
@@ -13901,7 +13918,7 @@
       <c r="AB7" s="17">
         <v>-0.2759264321806118</v>
       </c>
-      <c r="AC7" s="30">
+      <c r="AC7" s="27">
         <f>Y6</f>
         <v>2</v>
       </c>
@@ -13915,7 +13932,7 @@
       <c r="AH7" s="16">
         <v>3</v>
       </c>
-      <c r="AI7" s="31">
+      <c r="AI7" s="28">
         <f t="shared" si="1"/>
         <v>-0.3849286187770114</v>
       </c>
@@ -13925,7 +13942,7 @@
       <c r="AK7" s="17">
         <v>-7.3656107730099993E-2</v>
       </c>
-      <c r="AL7" s="30">
+      <c r="AL7" s="27">
         <f>AH6</f>
         <v>2</v>
       </c>
@@ -13981,7 +13998,7 @@
       <c r="Y8" s="16">
         <v>4</v>
       </c>
-      <c r="Z8" s="31">
+      <c r="Z8" s="28">
         <f t="shared" si="0"/>
         <v>-0.28592643218061181</v>
       </c>
@@ -13991,7 +14008,7 @@
       <c r="AB8" s="17">
         <v>0.20352189552526356</v>
       </c>
-      <c r="AC8" s="30">
+      <c r="AC8" s="27">
         <f>Y6</f>
         <v>2</v>
       </c>
@@ -14005,7 +14022,7 @@
       <c r="AH8" s="16">
         <v>4</v>
       </c>
-      <c r="AI8" s="31">
+      <c r="AI8" s="28">
         <f t="shared" si="1"/>
         <v>-0.3849286187770114</v>
       </c>
@@ -14015,7 +14032,7 @@
       <c r="AK8" s="17">
         <v>1.7615033682025305</v>
       </c>
-      <c r="AL8" s="30">
+      <c r="AL8" s="27">
         <f>AH6</f>
         <v>2</v>
       </c>
@@ -14065,7 +14082,7 @@
         <f>(F11-$M$5)/$M$5</f>
         <v>-0.14498353809622816</v>
       </c>
-      <c r="AC9" s="30">
+      <c r="AC9" s="27">
         <f>Y7</f>
         <v>3</v>
       </c>
@@ -14073,7 +14090,7 @@
         <f>AA7</f>
         <v>-8.0320909626405285E-2</v>
       </c>
-      <c r="AL9" s="30">
+      <c r="AL9" s="27">
         <f>AH7</f>
         <v>3</v>
       </c>
@@ -14125,7 +14142,7 @@
       </c>
       <c r="Y10" s="16"/>
       <c r="Z10" s="16"/>
-      <c r="AC10" s="30">
+      <c r="AC10" s="27">
         <f>Y7</f>
         <v>3</v>
       </c>
@@ -14135,7 +14152,7 @@
       </c>
       <c r="AH10" s="16"/>
       <c r="AI10" s="16"/>
-      <c r="AL10" s="30">
+      <c r="AL10" s="27">
         <f>AH7</f>
         <v>3</v>
       </c>
@@ -14185,7 +14202,7 @@
         <f>(F13-$M$5)/$M$5</f>
         <v>5.1908974160972107E-2</v>
       </c>
-      <c r="AC11" s="30">
+      <c r="AC11" s="27">
         <f>Y8</f>
         <v>4</v>
       </c>
@@ -14193,7 +14210,7 @@
         <f>AA8</f>
         <v>1.4035673399938112E-2</v>
       </c>
-      <c r="AL11" s="30">
+      <c r="AL11" s="27">
         <f>AH8</f>
         <v>4</v>
       </c>
@@ -14245,7 +14262,7 @@
       </c>
       <c r="Y12" s="16"/>
       <c r="Z12" s="16"/>
-      <c r="AC12" s="30">
+      <c r="AC12" s="27">
         <f>Y8</f>
         <v>4</v>
       </c>
@@ -14255,7 +14272,7 @@
       </c>
       <c r="AH12" s="16"/>
       <c r="AI12" s="16"/>
-      <c r="AL12" s="30">
+      <c r="AL12" s="27">
         <f>AH8</f>
         <v>4</v>
       </c>
@@ -14528,7 +14545,7 @@
       <c r="Y33" s="16">
         <v>1</v>
       </c>
-      <c r="Z33" s="31">
+      <c r="Z33" s="28">
         <f>MIN($AA$33:$AB$36)-26%</f>
         <v>-0.36993494021257312</v>
       </c>
@@ -14538,7 +14555,7 @@
       <c r="AB33" s="17">
         <v>2.0239624696879037</v>
       </c>
-      <c r="AC33" s="30">
+      <c r="AC33" s="27">
         <f>Y33</f>
         <v>1</v>
       </c>
@@ -14552,7 +14569,7 @@
       <c r="AH33" s="16">
         <v>1</v>
       </c>
-      <c r="AI33" s="31">
+      <c r="AI33" s="28">
         <f>MIN($AJ$33:$AK$36)-38%</f>
         <v>-0.73597255211007784</v>
       </c>
@@ -14564,7 +14581,7 @@
         <f>U6</f>
         <v>4.5079599717251355</v>
       </c>
-      <c r="AL33" s="30">
+      <c r="AL33" s="27">
         <f>AH33</f>
         <v>1</v>
       </c>
@@ -14580,7 +14597,7 @@
       <c r="Y34" s="16">
         <v>2</v>
       </c>
-      <c r="Z34" s="31">
+      <c r="Z34" s="28">
         <f t="shared" ref="Z34:Z36" si="2">MIN($AA$33:$AB$36)-26%</f>
         <v>-0.36993494021257312</v>
       </c>
@@ -14590,7 +14607,7 @@
       <c r="AB34" s="17">
         <v>0.46031841454006128</v>
       </c>
-      <c r="AC34" s="30">
+      <c r="AC34" s="27">
         <f>Y33</f>
         <v>1</v>
       </c>
@@ -14604,7 +14621,7 @@
       <c r="AH34" s="16">
         <v>2</v>
       </c>
-      <c r="AI34" s="31">
+      <c r="AI34" s="28">
         <f t="shared" ref="AI34:AI36" si="3">MIN($AJ$33:$AK$36)-38%</f>
         <v>-0.73597255211007784</v>
       </c>
@@ -14616,7 +14633,7 @@
         <f>U8</f>
         <v>0.57491039408683964</v>
       </c>
-      <c r="AL34" s="30">
+      <c r="AL34" s="27">
         <f>AH33</f>
         <v>1</v>
       </c>
@@ -14632,7 +14649,7 @@
       <c r="Y35" s="16">
         <v>3</v>
       </c>
-      <c r="Z35" s="31">
+      <c r="Z35" s="28">
         <f t="shared" si="2"/>
         <v>-0.36993494021257312</v>
       </c>
@@ -14642,7 +14659,7 @@
       <c r="AB35" s="17">
         <v>0.59557946837396036</v>
       </c>
-      <c r="AC35" s="30">
+      <c r="AC35" s="27">
         <f>Y34</f>
         <v>2</v>
       </c>
@@ -14656,7 +14673,7 @@
       <c r="AH35" s="16">
         <v>3</v>
       </c>
-      <c r="AI35" s="31">
+      <c r="AI35" s="28">
         <f t="shared" si="3"/>
         <v>-0.73597255211007784</v>
       </c>
@@ -14668,7 +14685,7 @@
         <f>U10</f>
         <v>-0.35597255211007783</v>
       </c>
-      <c r="AL35" s="30">
+      <c r="AL35" s="27">
         <f>AH34</f>
         <v>2</v>
       </c>
@@ -14684,7 +14701,7 @@
       <c r="Y36" s="16">
         <v>4</v>
       </c>
-      <c r="Z36" s="31">
+      <c r="Z36" s="28">
         <f t="shared" si="2"/>
         <v>-0.36993494021257312</v>
       </c>
@@ -14694,7 +14711,7 @@
       <c r="AB36" s="17">
         <v>2.1736250964361186</v>
       </c>
-      <c r="AC36" s="30">
+      <c r="AC36" s="27">
         <f>Y34</f>
         <v>2</v>
       </c>
@@ -14708,7 +14725,7 @@
       <c r="AH36" s="16">
         <v>4</v>
       </c>
-      <c r="AI36" s="31">
+      <c r="AI36" s="28">
         <f t="shared" si="3"/>
         <v>-0.73597255211007784</v>
       </c>
@@ -14720,7 +14737,7 @@
         <f>U12</f>
         <v>3.9772269087838268</v>
       </c>
-      <c r="AL36" s="30">
+      <c r="AL36" s="27">
         <f>AH34</f>
         <v>2</v>
       </c>
@@ -14730,7 +14747,7 @@
       </c>
     </row>
     <row r="37" spans="24:39" x14ac:dyDescent="0.25">
-      <c r="AC37" s="30">
+      <c r="AC37" s="27">
         <f>Y35</f>
         <v>3</v>
       </c>
@@ -14738,7 +14755,7 @@
         <f>AA35</f>
         <v>-0.10993494021257308</v>
       </c>
-      <c r="AL37" s="30">
+      <c r="AL37" s="27">
         <f>AH35</f>
         <v>3</v>
       </c>
@@ -14750,7 +14767,7 @@
     <row r="38" spans="24:39" x14ac:dyDescent="0.25">
       <c r="Y38" s="16"/>
       <c r="Z38" s="16"/>
-      <c r="AC38" s="30">
+      <c r="AC38" s="27">
         <f>Y35</f>
         <v>3</v>
       </c>
@@ -14760,7 +14777,7 @@
       </c>
       <c r="AH38" s="16"/>
       <c r="AI38" s="16"/>
-      <c r="AL38" s="30">
+      <c r="AL38" s="27">
         <f>AH35</f>
         <v>3</v>
       </c>
@@ -14770,7 +14787,7 @@
       </c>
     </row>
     <row r="39" spans="24:39" x14ac:dyDescent="0.25">
-      <c r="AC39" s="30">
+      <c r="AC39" s="27">
         <f>Y36</f>
         <v>4</v>
       </c>
@@ -14778,7 +14795,7 @@
         <f>AA36</f>
         <v>2.0938509024440652E-3</v>
       </c>
-      <c r="AL39" s="30">
+      <c r="AL39" s="27">
         <f>AH36</f>
         <v>4</v>
       </c>
@@ -14790,7 +14807,7 @@
     <row r="40" spans="24:39" x14ac:dyDescent="0.25">
       <c r="Y40" s="16"/>
       <c r="Z40" s="16"/>
-      <c r="AC40" s="30">
+      <c r="AC40" s="27">
         <f>Y36</f>
         <v>4</v>
       </c>
@@ -14800,7 +14817,7 @@
       </c>
       <c r="AH40" s="16"/>
       <c r="AI40" s="16"/>
-      <c r="AL40" s="30">
+      <c r="AL40" s="27">
         <f>AH36</f>
         <v>4</v>
       </c>
@@ -14811,8 +14828,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L4" r:id="rId1" display="mAP@50" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="M4" r:id="rId2" display="mAP@50-95" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="L4" r:id="rId1" display="mAP@50"/>
+    <hyperlink ref="M4" r:id="rId2" display="mAP@50-95"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
@@ -14820,7 +14837,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15649,15 +15666,15 @@
       <c r="U21" t="s">
         <v>95</v>
       </c>
-      <c r="V21" s="28">
+      <c r="V21" s="26">
         <f t="shared" ref="V21:V32" si="3">ROUND(F8-IF(B8="S",$F$5,IF(B8="M",$F$6,$F$7)),2)</f>
         <v>-0.14000000000000001</v>
       </c>
-      <c r="W21" s="28">
+      <c r="W21" s="26">
         <f t="shared" ref="W21:W32" si="4">ROUND(G8-IF(B8="S",$G$5,IF(B8="M",$G$6,$G$7)),2)</f>
         <v>0.77</v>
       </c>
-      <c r="X21" s="28">
+      <c r="X21" s="26">
         <f t="shared" ref="X21:X32" si="5">ROUND(H8-IF(B8="S",$H$5,IF(B8="M",$H$6,$H$7)),2)</f>
         <v>0.43</v>
       </c>
@@ -15666,15 +15683,15 @@
       <c r="U22" t="s">
         <v>96</v>
       </c>
-      <c r="V22" s="28">
+      <c r="V22" s="26">
         <f t="shared" si="3"/>
         <v>-0.15</v>
       </c>
-      <c r="W22" s="28">
+      <c r="W22" s="26">
         <f t="shared" si="4"/>
         <v>0.72</v>
       </c>
-      <c r="X22" s="28">
+      <c r="X22" s="26">
         <f t="shared" si="5"/>
         <v>0.61</v>
       </c>
@@ -15683,15 +15700,15 @@
       <c r="U23" t="s">
         <v>97</v>
       </c>
-      <c r="V23" s="28">
+      <c r="V23" s="26">
         <f t="shared" si="3"/>
         <v>-0.03</v>
       </c>
-      <c r="W23" s="28">
+      <c r="W23" s="26">
         <f t="shared" si="4"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="X23" s="28">
+      <c r="X23" s="26">
         <f t="shared" si="5"/>
         <v>0.53</v>
       </c>
@@ -15700,15 +15717,15 @@
       <c r="U24" t="s">
         <v>87</v>
       </c>
-      <c r="V24" s="28">
+      <c r="V24" s="26">
         <f t="shared" si="3"/>
         <v>0.05</v>
       </c>
-      <c r="W24" s="28">
+      <c r="W24" s="26">
         <f t="shared" si="4"/>
         <v>0.16</v>
       </c>
-      <c r="X24" s="28">
+      <c r="X24" s="26">
         <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
@@ -15732,15 +15749,15 @@
       <c r="U25" t="s">
         <v>88</v>
       </c>
-      <c r="V25" s="28">
+      <c r="V25" s="26">
         <f t="shared" si="3"/>
         <v>-0.17</v>
       </c>
-      <c r="W25" s="28">
+      <c r="W25" s="26">
         <f t="shared" si="4"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="X25" s="28">
+      <c r="X25" s="26">
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
@@ -15764,15 +15781,15 @@
       <c r="U26" t="s">
         <v>86</v>
       </c>
-      <c r="V26" s="28">
+      <c r="V26" s="26">
         <f t="shared" si="3"/>
         <v>-0.27</v>
       </c>
-      <c r="W26" s="28">
+      <c r="W26" s="26">
         <f t="shared" si="4"/>
         <v>0.09</v>
       </c>
-      <c r="X26" s="28">
+      <c r="X26" s="26">
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
@@ -15797,15 +15814,15 @@
       <c r="U27" t="s">
         <v>89</v>
       </c>
-      <c r="V27" s="28">
+      <c r="V27" s="26">
         <f t="shared" si="3"/>
         <v>0.18</v>
       </c>
-      <c r="W27" s="28">
+      <c r="W27" s="26">
         <f t="shared" si="4"/>
         <v>0.08</v>
       </c>
-      <c r="X27" s="28">
+      <c r="X27" s="26">
         <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
@@ -15829,15 +15846,15 @@
       <c r="U28" t="s">
         <v>90</v>
       </c>
-      <c r="V28" s="28">
+      <c r="V28" s="26">
         <f t="shared" si="3"/>
         <v>-0.38</v>
       </c>
-      <c r="W28" s="28">
+      <c r="W28" s="26">
         <f t="shared" si="4"/>
         <v>0.27</v>
       </c>
-      <c r="X28" s="28">
+      <c r="X28" s="26">
         <f t="shared" si="5"/>
         <v>0.26</v>
       </c>
@@ -15861,15 +15878,15 @@
       <c r="U29" t="s">
         <v>91</v>
       </c>
-      <c r="V29" s="28">
+      <c r="V29" s="26">
         <f t="shared" si="3"/>
         <v>-0.4</v>
       </c>
-      <c r="W29" s="28">
+      <c r="W29" s="26">
         <f t="shared" si="4"/>
         <v>0.23</v>
       </c>
-      <c r="X29" s="28">
+      <c r="X29" s="26">
         <f t="shared" si="5"/>
         <v>0.19</v>
       </c>
@@ -15896,15 +15913,15 @@
       <c r="U30" t="s">
         <v>92</v>
       </c>
-      <c r="V30" s="28">
+      <c r="V30" s="26">
         <f t="shared" si="3"/>
         <v>-0.03</v>
       </c>
-      <c r="W30" s="28">
+      <c r="W30" s="26">
         <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
-      <c r="X30" s="28">
+      <c r="X30" s="26">
         <f t="shared" si="5"/>
         <v>0.46</v>
       </c>
@@ -15928,15 +15945,15 @@
       <c r="U31" t="s">
         <v>93</v>
       </c>
-      <c r="V31" s="28">
+      <c r="V31" s="26">
         <f t="shared" si="3"/>
         <v>-0.11</v>
       </c>
-      <c r="W31" s="28">
+      <c r="W31" s="26">
         <f t="shared" si="4"/>
         <v>0.61</v>
       </c>
-      <c r="X31" s="28">
+      <c r="X31" s="26">
         <f t="shared" si="5"/>
         <v>0.56999999999999995</v>
       </c>
@@ -15960,15 +15977,15 @@
       <c r="U32" t="s">
         <v>94</v>
       </c>
-      <c r="V32" s="28">
+      <c r="V32" s="26">
         <f t="shared" si="3"/>
         <v>-0.03</v>
       </c>
-      <c r="W32" s="28">
+      <c r="W32" s="26">
         <f t="shared" si="4"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="X32" s="28">
+      <c r="X32" s="26">
         <f t="shared" si="5"/>
         <v>0.54</v>
       </c>
